--- a/results/job_matches_2026-03-17.xlsx
+++ b/results/job_matches_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,52 +503,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer &amp; Architect</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fd769b82cca737f</t>
+          <t>https://www.indeed.com/viewjob?jk=342faa6b5c9756a2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior Data Engineer &amp; Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d6dc4080863d025</t>
+          <t>https://www.indeed.com/viewjob?jk=6fd769b82cca737f</t>
         </is>
       </c>
     </row>
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9486e542e0314630</t>
+          <t>https://www.indeed.com/viewjob?jk=4d6dc4080863d025</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b271d311d5d546b6</t>
+          <t>https://www.indeed.com/viewjob?jk=9486e542e0314630</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d1545b725cacf9</t>
+          <t>https://www.indeed.com/viewjob?jk=b271d311d5d546b6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e62fa620ec25df7</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d1545b725cacf9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer with Python</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0b74cae84f6befa</t>
+          <t>https://www.indeed.com/viewjob?jk=6e62fa620ec25df7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Data Engineer with Python</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9727641069e970c0</t>
+          <t>https://www.indeed.com/viewjob?jk=c0b74cae84f6befa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8674e111f05b66a1</t>
+          <t>https://www.indeed.com/viewjob?jk=9727641069e970c0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CPI Security</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e81977d38af04d</t>
+          <t>https://www.indeed.com/viewjob?jk=8674e111f05b66a1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kafka Data Streaming Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, IAM, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24db9c74d80b856c</t>
+          <t>https://www.indeed.com/viewjob?jk=c8e81977d38af04d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Kafka Data Streaming Consultant</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, ECS, RDS, Azure, Databricks, Cloud Storage</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e7128e441d147a</t>
+          <t>https://www.indeed.com/viewjob?jk=24db9c74d80b856c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, ECS, RDS, Azure, Databricks, Cloud Storage</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5861e377dbf3fbc8</t>
+          <t>https://www.indeed.com/viewjob?jk=33e7128e441d147a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd06ecb9103a776</t>
+          <t>https://www.indeed.com/viewjob?jk=5861e377dbf3fbc8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52c30ca213c085f</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd06ecb9103a776</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8d99a7003ab349</t>
+          <t>https://www.indeed.com/viewjob?jk=c52c30ca213c085f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>(1383) Senior SRE/DevOps Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nearsure</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, SQL Server, DynamoDB, NoSQL, Jenkins, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8598ff2a82d03277</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8d99a7003ab349</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IAM Helpdesk Analyst</t>
+          <t>(1383) Senior SRE/DevOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Nearsure</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, API Gateway, IAM, Scala</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, SQL Server, DynamoDB, NoSQL, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5dd84afd435111</t>
+          <t>https://www.indeed.com/viewjob?jk=8598ff2a82d03277</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>IAM Helpdesk Analyst</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sun Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, API Gateway, IAM, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1e43a65f53e347c</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5dd84afd435111</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Participant Communication Services (PCS) Platform Architect - Virtual</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, ECS, RDS, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02bd3db44eac42a0</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ed89084b43969d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Sun Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e43a65f53e347c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer - TS/SCI with Polygraph</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
+          <t>https://www.indeed.com/viewjob?jk=02bd3db44eac42a0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=407c52d9f78d8a4a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Production Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bdd4694bf19ea44</t>
+          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Software Engineer - TS/SCI with Polygraph</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1527cf38b699a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Network Engineer</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1392,11 +1392,11 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, Spark, Scala</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7aa69b55de4760</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Network Operations Trainee</t>
+          <t>Senior Production Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Legion</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88bda3516bc06812</t>
+          <t>https://www.indeed.com/viewjob?jk=8bdd4694bf19ea44</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1811a5e61116c3b5</t>
+          <t>https://www.indeed.com/viewjob?jk=f1527cf38b699a4d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Network Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, Spark, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f37aff04bbbf14</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7aa69b55de4760</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Network Operations Trainee</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b6861263b7736a</t>
+          <t>https://www.indeed.com/viewjob?jk=88bda3516bc06812</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a0e777ff5549418</t>
+          <t>https://www.indeed.com/viewjob?jk=1811a5e61116c3b5</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6027f8f887b28cc</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f37aff04bbbf14</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Java Consultant</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b6861263b7736a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=239b1046f06d3d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=4a0e777ff5549418</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a7f6dab575a97ad</t>
+          <t>https://www.indeed.com/viewjob?jk=f6027f8f887b28cc</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02a598ce56d257c</t>
+          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Kafka Operations Administrator</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b64bf3747c350d3</t>
+          <t>https://www.indeed.com/viewjob?jk=f208993ee2fdbe1c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Java Consultant</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FundMate LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d833bbf779bc5e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
         </is>
       </c>
     </row>
@@ -2008,25 +2008,25 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
+          <t>https://www.indeed.com/viewjob?jk=239b1046f06d3d2f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
+          <t>https://www.indeed.com/viewjob?jk=3a7f6dab575a97ad</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Solution Design Focused</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>UnyBrands</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d83c96f81842df2</t>
+          <t>https://www.indeed.com/viewjob?jk=d02a598ce56d257c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer – Ontology &amp; Semantic Modeling</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SoundThinking</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d5fa75dac6e177</t>
+          <t>https://www.indeed.com/viewjob?jk=0b64bf3747c350d3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Consultant, Data Management</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Beghou Consulting</t>
+          <t>FundMate LLC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1564012a6ce57a97</t>
+          <t>https://www.indeed.com/viewjob?jk=d833bbf779bc5e9f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=929003fb57aecac9</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab66e7fa68e90c6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, PostgreSQL, MySQL, MongoDB, NoSQL, Jenkins, Maven, Docker</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f452a32fedc556a0</t>
+          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Operations Analytics Data Scientist</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RadNet</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Kafka Administrator</t>
+          <t>Senior Data Engineer Solution Design Focused</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>UnyBrands</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
+          <t>https://www.indeed.com/viewjob?jk=6d83c96f81842df2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DBHDS - SQL Database Administrator</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Betis Group, Inc.</t>
+          <t>Knightscope, Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
+          <t>https://www.indeed.com/viewjob?jk=929003fb57aecac9</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Kimco Realty Corporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, PostgreSQL, MySQL, MongoDB, NoSQL, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=f452a32fedc556a0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Application Developer Sr II</t>
+          <t>Operations Analytics Data Scientist</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>RadNet</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
+          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Application Developer Sr I</t>
+          <t>Kafka Administrator</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
+          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>DBHDS - SQL Database Administrator</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Betis Group, Inc.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=016f2662bb776d79</t>
+          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SQL DBA/ Data Engineer- AWS Migration</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Kimco Realty Corporation</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
+          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
+          <t>Application Developer Sr II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Welltower, Inc</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
+          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Application Developer Sr I</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Skywalk Global</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c074eb3bed74ad</t>
+          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2626,29 +2626,29 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=016f2662bb776d79</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>SQL DBA/ Data Engineer- AWS Migration</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Excelsior University</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
+          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
+          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Welltower, Inc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a1692fa5839e7a</t>
+          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Skywalk Global</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c074eb3bed74ad</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
+          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
+          <t>https://www.indeed.com/viewjob?jk=04a1692fa5839e7a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,14 +2841,14 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
+          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AI Industry 5.0 Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Bloom Energy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, Tableau, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd1a549fc1388c4</t>
+          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>adswizz</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,19 +2946,19 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
+          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2967,11 +2967,11 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,102 +2981,102 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EverCommerce - Sr. BI Engineer</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, Power BI, Tableau</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96fcb774adfa1d8f</t>
+          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Excelsior University</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
+          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>AI Industry 5.0 Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>Bloom Energy</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, Tableau, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd1a549fc1388c4</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>adswizz</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
+          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
+          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>EverCommerce - Sr. BI Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
+          <t>https://www.indeed.com/viewjob?jk=96fcb774adfa1d8f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BI Engineer , BI Center of Excellence</t>
+          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Evolent</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
+          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Kafka Cluster Support Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TeraWatt Infrastructure</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
+          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
         </is>
       </c>
     </row>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
+          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Networking Trainee</t>
+          <t>BI Engineer , BI Center of Excellence</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Evolent</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Azure Databricks with IDMC experience</t>
+          <t>Kafka Cluster Support Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Dimensional Modeling, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d268eef1366883</t>
+          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Consultant, Data Management</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Beghou Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Databricks, Spark, PySpark, Snowflake, Oracle, PostgreSQL, MySQL, ETL, Power BI, Tableau</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb1560a6c29ae4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,14 +3506,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Kafka Production Support Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
+          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
+          <t>Networking Trainee</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Senior Software Engineer, (.NET)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foundation Source</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>AWS, S3, RDS, Scala, MySQL, CI/CD, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
+          <t>https://www.indeed.com/viewjob?jk=8d566d00eb2e403d</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Commercial Operations BI Analyst</t>
+          <t>DATA SCIENTIST</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Tableau, Git, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
+          <t>https://www.indeed.com/viewjob?jk=c81ccc2c8f052915</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Security Consultant</t>
+          <t>Azure Databricks with IDMC experience</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,17 +3671,297 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Dimensional Modeling, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78d268eef1366883</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>RELX Group</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>RDS, Scala, PostgreSQL, DynamoDB, Splunk, CI/CD, Jenkins, Jenkins, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12e386150a46a2a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Kafka Production Support Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Bank of America</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Kafka</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Commercial Operations BI Analyst</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Colgate-Palmolive</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Piscataway, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Security Consultant</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
           <t>Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=aa7381f71e38e6eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38b2be41415df8a0</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-17.xlsx
+++ b/results/job_matches_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer &amp; Architect</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fd769b82cca737f</t>
+          <t>https://www.indeed.com/viewjob?jk=4d6dc4080863d025</t>
         </is>
       </c>
     </row>
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d6dc4080863d025</t>
+          <t>https://www.indeed.com/viewjob?jk=9486e542e0314630</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9486e542e0314630</t>
+          <t>https://www.indeed.com/viewjob?jk=b271d311d5d546b6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b271d311d5d546b6</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d1545b725cacf9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d1545b725cacf9</t>
+          <t>https://www.indeed.com/viewjob?jk=6e62fa620ec25df7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Data Engineer with Python</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e62fa620ec25df7</t>
+          <t>https://www.indeed.com/viewjob?jk=c0b74cae84f6befa</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer with Python</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0b74cae84f6befa</t>
+          <t>https://www.indeed.com/viewjob?jk=9727641069e970c0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9727641069e970c0</t>
+          <t>https://www.indeed.com/viewjob?jk=8674e111f05b66a1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, IAM, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8674e111f05b66a1</t>
+          <t>https://www.indeed.com/viewjob?jk=c8e81977d38af04d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kafka Data Streaming Consultant</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CPI Security</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e81977d38af04d</t>
+          <t>https://www.indeed.com/viewjob?jk=24db9c74d80b856c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kafka Data Streaming Consultant</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, ECS, RDS, Azure, Databricks, Cloud Storage</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24db9c74d80b856c</t>
+          <t>https://www.indeed.com/viewjob?jk=33e7128e441d147a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, ECS, RDS, Azure, Databricks, Cloud Storage</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e7128e441d147a</t>
+          <t>https://www.indeed.com/viewjob?jk=5861e377dbf3fbc8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5861e377dbf3fbc8</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd06ecb9103a776</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd06ecb9103a776</t>
+          <t>https://www.indeed.com/viewjob?jk=c52c30ca213c085f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52c30ca213c085f</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8d99a7003ab349</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>(1383) Senior SRE/DevOps Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>Nearsure</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, SQL Server, DynamoDB, NoSQL, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8d99a7003ab349</t>
+          <t>https://www.indeed.com/viewjob?jk=8598ff2a82d03277</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>(1383) Senior SRE/DevOps Engineer</t>
+          <t>IAM Helpdesk Analyst</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nearsure</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, SQL Server, DynamoDB, NoSQL, Jenkins, Terraform</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, API Gateway, IAM, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8598ff2a82d03277</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5dd84afd435111</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IAM Helpdesk Analyst</t>
+          <t>Participant Communication Services (PCS) Platform Architect - Virtual</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, API Gateway, IAM, Scala</t>
+          <t>AWS, ECS, RDS, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5dd84afd435111</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ed89084b43969d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Participant Communication Services (PCS) Platform Architect - Virtual</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ed89084b43969d</t>
+          <t>https://www.indeed.com/viewjob?jk=02bd3db44eac42a0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sun Group</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1e43a65f53e347c</t>
+          <t>https://www.indeed.com/viewjob?jk=407c52d9f78d8a4a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02bd3db44eac42a0</t>
+          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Software Engineer - TS/SCI with Polygraph</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=407c52d9f78d8a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer - TS/SCI with Polygraph</t>
+          <t>Senior Production Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Legion</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
+          <t>https://www.indeed.com/viewjob?jk=8bdd4694bf19ea44</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1392,11 +1392,11 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=f1527cf38b699a4d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Production Engineer</t>
+          <t>Network Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, Spark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bdd4694bf19ea44</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7aa69b55de4760</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Network Operations Trainee</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1527cf38b699a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=88bda3516bc06812</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Network Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7aa69b55de4760</t>
+          <t>https://www.indeed.com/viewjob?jk=1811a5e61116c3b5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Network Operations Trainee</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88bda3516bc06812</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f37aff04bbbf14</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1811a5e61116c3b5</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b6861263b7736a</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f37aff04bbbf14</t>
+          <t>https://www.indeed.com/viewjob?jk=4a0e777ff5549418</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b6861263b7736a</t>
+          <t>https://www.indeed.com/viewjob?jk=f6027f8f887b28cc</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Kafka Operations Administrator</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a0e777ff5549418</t>
+          <t>https://www.indeed.com/viewjob?jk=f208993ee2fdbe1c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6027f8f887b28cc</t>
+          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Java Consultant</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
+          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Kafka Operations Administrator</t>
+          <t>Backend Developer - .NET &amp; Azure</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Reidy</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f208993ee2fdbe1c</t>
+          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Java Consultant</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Backend Developer - .NET &amp; Azure</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Reidy</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>Azure, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
+          <t>https://www.indeed.com/viewjob?jk=4181653d522a2852</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,14 +1896,14 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=4379abeabd8c87ca</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Kafka Data Replication Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
+          <t>AWS, Lambda, S3, ECS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4181653d522a2852</t>
+          <t>https://www.indeed.com/viewjob?jk=4c99b3c52b9b8bc7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4379abeabd8c87ca</t>
+          <t>https://www.indeed.com/viewjob?jk=239b1046f06d3d2f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Kafka Data Replication Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c99b3c52b9b8bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=3a7f6dab575a97ad</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=239b1046f06d3d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=d02a598ce56d257c</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a7f6dab575a97ad</t>
+          <t>https://www.indeed.com/viewjob?jk=0b64bf3747c350d3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>FundMate LLC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02a598ce56d257c</t>
+          <t>https://www.indeed.com/viewjob?jk=d833bbf779bc5e9f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, S3, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b64bf3747c350d3</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab66e7fa68e90c6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FundMate LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Jenkins</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d833bbf779bc5e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab66e7fa68e90c6</t>
+          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Senior Data Engineer Solution Design Focused</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>UnyBrands</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
+          <t>https://www.indeed.com/viewjob?jk=6d83c96f81842df2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Knightscope, Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
+          <t>https://www.indeed.com/viewjob?jk=929003fb57aecac9</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Solution Design Focused</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>UnyBrands</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Google Cloud Platform, PostgreSQL, MySQL, MongoDB, NoSQL, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d83c96f81842df2</t>
+          <t>https://www.indeed.com/viewjob?jk=f452a32fedc556a0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Operations Analytics Data Scientist</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>RadNet</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,14 +2351,14 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=929003fb57aecac9</t>
+          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Kafka Administrator</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2372,11 +2372,11 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, PostgreSQL, MySQL, MongoDB, NoSQL, Jenkins, Maven, Docker</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f452a32fedc556a0</t>
+          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Operations Analytics Data Scientist</t>
+          <t>DBHDS - SQL Database Administrator</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RadNet</t>
+          <t>Betis Group, Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Kafka Administrator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kimco Realty Corporation</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
+          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DBHDS - SQL Database Administrator</t>
+          <t>Application Developer Sr II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Betis Group, Inc.</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
+          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Application Developer Sr I</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Kimco Realty Corporation</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Application Developer Sr II</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
+          <t>https://www.indeed.com/viewjob?jk=016f2662bb776d79</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Application Developer Sr I</t>
+          <t>SQL DBA/ Data Engineer- AWS Migration</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
+          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Welltower, Inc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,19 +2631,19 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=016f2662bb776d79</t>
+          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SQL DBA/ Data Engineer- AWS Migration</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Skywalk Global</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c074eb3bed74ad</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Welltower, Inc</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
+          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Skywalk Global</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c074eb3bed74ad</t>
+          <t>https://www.indeed.com/viewjob?jk=04a1692fa5839e7a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a1692fa5839e7a</t>
+          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,14 +2841,14 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
+          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
+          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
         </is>
       </c>
     </row>
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
+          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Excelsior University</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
+          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>AI Industry 5.0 Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Bloom Energy</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, Tableau, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd1a549fc1388c4</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Excelsior University</t>
+          <t>adswizz</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
+          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI Industry 5.0 Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Bloom Energy</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, Tableau, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd1a549fc1388c4</t>
+          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>adswizz</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
+          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>TeraWatt Infrastructure</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EverCommerce - Sr. BI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96fcb774adfa1d8f</t>
+          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
+          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
+          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>BI Engineer , BI Center of Excellence</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Evolent</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,14 +3296,14 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
+          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Kafka Cluster Support Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
+          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
+          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BI Engineer , BI Center of Excellence</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Evolent</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,14 +3401,14 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
+          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Kafka Cluster Support Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
+          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Networking Trainee</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Software Engineer, (.NET)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foundation Source</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>AWS, S3, RDS, Scala, MySQL, CI/CD, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=8d566d00eb2e403d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Scala, PostgreSQL, DynamoDB, Splunk, CI/CD, Jenkins, Jenkins, SonarQube, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
+          <t>https://www.indeed.com/viewjob?jk=12e386150a46a2a5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Networking Trainee</t>
+          <t>DATA SCIENTIST</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Tableau, Git, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=c81ccc2c8f052915</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, (.NET)</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Foundation Source</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, MySQL, CI/CD, Jenkins, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d566d00eb2e403d</t>
+          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>DATA SCIENTIST</t>
+          <t>Kafka Production Support Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Tableau, Git, Python, SQL, Scala</t>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c81ccc2c8f052915</t>
+          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Azure Databricks with IDMC experience</t>
+          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Dimensional Modeling, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d268eef1366883</t>
+          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, DynamoDB, Splunk, CI/CD, Jenkins, Jenkins, SonarQube, Git</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12e386150a46a2a5</t>
+          <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Commercial Operations BI Analyst</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Kafka Production Support Engineer</t>
+          <t>Business Intelligence Developer (Hybrid)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Westerra Credit Union</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
+          <t>https://www.indeed.com/viewjob?jk=ff473c63d82167e1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
+          <t>Security Consultant</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
+          <t>Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
+          <t>https://www.indeed.com/viewjob?jk=aa7381f71e38e6eb</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>AWS, Lambda, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3855,111 +3855,6 @@
         </is>
       </c>
       <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Commercial Operations BI Analyst</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Colgate-Palmolive</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Piscataway, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Security Consultant</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa7381f71e38e6eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>SAS</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=38b2be41415df8a0</t>
         </is>

--- a/results/job_matches_2026-03-17.xlsx
+++ b/results/job_matches_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer (Remote)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>Lyzr AI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Flume, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,77 +496,77 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36bcd88655ec26b</t>
+          <t>https://www.indeed.com/viewjob?jk=8a23265f32b23de3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, SQL Server</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=342faa6b5c9756a2</t>
+          <t>https://www.indeed.com/viewjob?jk=b36bcd88655ec26b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d6dc4080863d025</t>
+          <t>https://www.indeed.com/viewjob?jk=342faa6b5c9756a2</t>
         </is>
       </c>
     </row>
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9486e542e0314630</t>
+          <t>https://www.indeed.com/viewjob?jk=4d6dc4080863d025</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b271d311d5d546b6</t>
+          <t>https://www.indeed.com/viewjob?jk=9486e542e0314630</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d1545b725cacf9</t>
+          <t>https://www.indeed.com/viewjob?jk=b271d311d5d546b6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e62fa620ec25df7</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d1545b725cacf9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer with Python</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0b74cae84f6befa</t>
+          <t>https://www.indeed.com/viewjob?jk=6e62fa620ec25df7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Data Engineer with Python</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9727641069e970c0</t>
+          <t>https://www.indeed.com/viewjob?jk=c0b74cae84f6befa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8674e111f05b66a1</t>
+          <t>https://www.indeed.com/viewjob?jk=9727641069e970c0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CPI Security</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e81977d38af04d</t>
+          <t>https://www.indeed.com/viewjob?jk=8674e111f05b66a1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kafka Data Streaming Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, IAM, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24db9c74d80b856c</t>
+          <t>https://www.indeed.com/viewjob?jk=c8e81977d38af04d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Kafka Data Streaming Consultant</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, ECS, RDS, Azure, Databricks, Cloud Storage</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e7128e441d147a</t>
+          <t>https://www.indeed.com/viewjob?jk=24db9c74d80b856c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, ECS, RDS, Azure, Databricks, Cloud Storage</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5861e377dbf3fbc8</t>
+          <t>https://www.indeed.com/viewjob?jk=33e7128e441d147a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd06ecb9103a776</t>
+          <t>https://www.indeed.com/viewjob?jk=5861e377dbf3fbc8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52c30ca213c085f</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd06ecb9103a776</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8d99a7003ab349</t>
+          <t>https://www.indeed.com/viewjob?jk=c52c30ca213c085f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>(1383) Senior SRE/DevOps Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nearsure</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, SQL Server, DynamoDB, NoSQL, Jenkins, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8598ff2a82d03277</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8d99a7003ab349</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer - TS/SCI with Polygraph</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
+          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Software Engineer - TS/SCI with Polygraph</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Kafka Operations Administrator</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f208993ee2fdbe1c</t>
+          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Kafka Operations Administrator</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
+          <t>https://www.indeed.com/viewjob?jk=f208993ee2fdbe1c</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Backend Developer - .NET &amp; Azure</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Reidy</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>Azure, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
+          <t>https://www.indeed.com/viewjob?jk=4181653d522a2852</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,14 +1826,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=4379abeabd8c87ca</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Kafka Data Replication Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
+          <t>AWS, Lambda, S3, ECS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4181653d522a2852</t>
+          <t>https://www.indeed.com/viewjob?jk=4c99b3c52b9b8bc7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Backend Developer - .NET &amp; Azure</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Reidy</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4379abeabd8c87ca</t>
+          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Kafka Data Replication Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c99b3c52b9b8bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
         </is>
       </c>
     </row>
@@ -2253,17 +2253,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr. Data Engineer – Ontology &amp; Semantic Modeling</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>SoundThinking</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=929003fb57aecac9</t>
+          <t>https://www.indeed.com/viewjob?jk=02d5fa75dac6e177</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Knightscope, Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, PostgreSQL, MySQL, MongoDB, NoSQL, Jenkins, Maven, Docker</t>
+          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f452a32fedc556a0</t>
+          <t>https://www.indeed.com/viewjob?jk=929003fb57aecac9</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Operations Analytics Data Scientist</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RadNet</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
+          <t>AWS, Azure, Google Cloud Platform, PostgreSQL, MySQL, MongoDB, NoSQL, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=f452a32fedc556a0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Kafka Administrator</t>
+          <t>Operations Analytics Data Scientist</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RadNet</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
+          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DBHDS - SQL Database Administrator</t>
+          <t>Kafka Administrator</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Betis Group, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
+          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DBHDS - SQL Database Administrator</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Kimco Realty Corporation</t>
+          <t>Betis Group, Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Application Developer Sr II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Kimco Realty Corporation</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
+          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Application Developer Sr I</t>
+          <t>Application Developer Sr II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
+          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Application Developer Sr I</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=016f2662bb776d79</t>
+          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SQL DBA/ Data Engineer- AWS Migration</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
+          <t>https://www.indeed.com/viewjob?jk=016f2662bb776d79</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
+          <t>SQL DBA/ Data Engineer- AWS Migration</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Welltower, Inc</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
+          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Skywalk Global</t>
+          <t>Welltower, Inc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c074eb3bed74ad</t>
+          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Skywalk Global</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2696,29 +2696,29 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c074eb3bed74ad</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a1692fa5839e7a</t>
+          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
+          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
+          <t>https://www.indeed.com/viewjob?jk=04a1692fa5839e7a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,14 +2841,14 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
         </is>
       </c>
     </row>
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
+          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Excelsior University</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
+          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI Industry 5.0 Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Bloom Energy</t>
+          <t>Excelsior University</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, Tableau, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd1a549fc1388c4</t>
+          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>AI Industry 5.0 Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>adswizz</t>
+          <t>Bloom Energy</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, Tableau, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd1a549fc1388c4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>adswizz</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
+          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
+          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>TeraWatt Infrastructure</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
+          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
+          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
+          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BI Engineer , BI Center of Excellence</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Evolent</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
+          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Kafka Cluster Support Engineer</t>
+          <t>BI Engineer , BI Center of Excellence</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Evolent</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,14 +3331,14 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
+          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Kafka Cluster Support Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,14 +3366,14 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
+          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
+          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Networking Trainee</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, (.NET)</t>
+          <t>Networking Trainee</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Foundation Source</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, MySQL, CI/CD, Jenkins, Docker, Jenkins, Git</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d566d00eb2e403d</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I</t>
+          <t>Senior Software Engineer, (.NET)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Foundation Source</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,17 +3531,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, DynamoDB, Splunk, CI/CD, Jenkins, Jenkins, SonarQube, Git</t>
+          <t>AWS, S3, RDS, Scala, MySQL, CI/CD, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12e386150a46a2a5</t>
+          <t>https://www.indeed.com/viewjob?jk=8d566d00eb2e403d</t>
         </is>
       </c>
     </row>
@@ -3583,17 +3583,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
+          <t>RDS, Scala, PostgreSQL, DynamoDB, Splunk, CI/CD, Jenkins, Jenkins, SonarQube, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=12e386150a46a2a5</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Kafka Production Support Engineer</t>
+          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
+          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,14 +3681,14 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
+          <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Kafka Production Support Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
+          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Commercial Operations BI Analyst</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
+          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer (Hybrid)</t>
+          <t>Commercial Operations BI Analyst</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Westerra Credit Union</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff473c63d82167e1</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Security Consultant</t>
+          <t>Business Intelligence Developer (Hybrid)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Westerra Credit Union</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
+          <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa7381f71e38e6eb</t>
+          <t>https://www.indeed.com/viewjob?jk=ff473c63d82167e1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Security Consultant</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SAS</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,15 +3846,50 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
+          <t>Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa7381f71e38e6eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
           <t>AWS, Lambda, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=38b2be41415df8a0</t>
         </is>

--- a/results/job_matches_2026-03-17.xlsx
+++ b/results/job_matches_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Big Data Engineer - AWS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>Purple Austyn Technologies</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8d99a7003ab349</t>
+          <t>https://www.indeed.com/viewjob?jk=943257051095e0f6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IAM Helpdesk Analyst</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, API Gateway, IAM, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5dd84afd435111</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8d99a7003ab349</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Participant Communication Services (PCS) Platform Architect - Virtual</t>
+          <t>IAM Helpdesk Analyst</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, API Gateway, IAM, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ed89084b43969d</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5dd84afd435111</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Participant Communication Services (PCS) Platform Architect - Virtual</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, ECS, RDS, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02bd3db44eac42a0</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ed89084b43969d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=407c52d9f78d8a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=02bd3db44eac42a0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=407c52d9f78d8a4a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer - TS/SCI with Polygraph</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
+          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Production Engineer</t>
+          <t>Software Engineer - TS/SCI with Polygraph</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bdd4694bf19ea44</t>
+          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Senior Production Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Legion</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1527cf38b699a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=8bdd4694bf19ea44</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Network Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, Spark, Scala</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7aa69b55de4760</t>
+          <t>https://www.indeed.com/viewjob?jk=f1527cf38b699a4d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Network Operations Trainee</t>
+          <t>Network Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, Spark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88bda3516bc06812</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7aa69b55de4760</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Network Operations Trainee</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1811a5e61116c3b5</t>
+          <t>https://www.indeed.com/viewjob?jk=88bda3516bc06812</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Kafka Operations Administrator</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f37aff04bbbf14</t>
+          <t>https://www.indeed.com/viewjob?jk=f208993ee2fdbe1c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b6861263b7736a</t>
+          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>Azure, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a0e777ff5549418</t>
+          <t>https://www.indeed.com/viewjob?jk=4181653d522a2852</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6027f8f887b28cc</t>
+          <t>https://www.indeed.com/viewjob?jk=4379abeabd8c87ca</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Kafka Data Replication Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
+          <t>https://www.indeed.com/viewjob?jk=4c99b3c52b9b8bc7</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Kafka Operations Administrator</t>
+          <t>Java Consultant</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f208993ee2fdbe1c</t>
+          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Java Consultant</t>
+          <t>Backend Developer - .NET &amp; Azure</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Reidy</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4181653d522a2852</t>
+          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4379abeabd8c87ca</t>
+          <t>https://www.indeed.com/viewjob?jk=239b1046f06d3d2f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Kafka Data Replication Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c99b3c52b9b8bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=3a7f6dab575a97ad</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Backend Developer - .NET &amp; Azure</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Reidy</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
+          <t>https://www.indeed.com/viewjob?jk=d02a598ce56d257c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=0b64bf3747c350d3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>FundMate LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=239b1046f06d3d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=d833bbf779bc5e9f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, S3, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a7f6dab575a97ad</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab66e7fa68e90c6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02a598ce56d257c</t>
+          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b64bf3747c350d3</t>
+          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Senior Data Engineer Solution Design Focused</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FundMate LLC</t>
+          <t>UnyBrands</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d833bbf779bc5e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=6d83c96f81842df2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Knightscope, Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab66e7fa68e90c6</t>
+          <t>https://www.indeed.com/viewjob?jk=929003fb57aecac9</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Azure, Google Cloud Platform, PostgreSQL, MySQL, MongoDB, NoSQL, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
+          <t>https://www.indeed.com/viewjob?jk=f452a32fedc556a0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Operations Analytics Data Scientist</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RadNet</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
+          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Solution Design Focused</t>
+          <t>Kafka Administrator</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>UnyBrands</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d83c96f81842df2</t>
+          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer – Ontology &amp; Semantic Modeling</t>
+          <t>DBHDS - SQL Database Administrator</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SoundThinking</t>
+          <t>Betis Group, Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d5fa75dac6e177</t>
+          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>Kimco Realty Corporation</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=929003fb57aecac9</t>
+          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Application Developer Sr II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, PostgreSQL, MySQL, MongoDB, NoSQL, Jenkins, Maven, Docker</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f452a32fedc556a0</t>
+          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Operations Analytics Data Scientist</t>
+          <t>Application Developer Sr I</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RadNet</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,14 +2386,14 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Kafka Administrator</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,19 +2421,19 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
+          <t>https://www.indeed.com/viewjob?jk=016f2662bb776d79</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DBHDS - SQL Database Administrator</t>
+          <t>SQL DBA/ Data Engineer- AWS Migration</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Betis Group, Inc.</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
+          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Kimco Realty Corporation</t>
+          <t>Welltower, Inc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Application Developer Sr II</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
+          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Application Developer Sr I</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
+          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=016f2662bb776d79</t>
+          <t>https://www.indeed.com/viewjob?jk=04a1692fa5839e7a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SQL DBA/ Data Engineer- AWS Migration</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Welltower, Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
+          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Skywalk Global</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c074eb3bed74ad</t>
+          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Excelsior University</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a1692fa5839e7a</t>
+          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>AI Industry 5.0 Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bloom Energy</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, Tableau, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd1a549fc1388c4</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>adswizz</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,19 +2876,19 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
+          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2897,11 +2897,11 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,67 +2911,67 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
+          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TeraWatt Infrastructure</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Excelsior University</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
+          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AI Industry 5.0 Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Bloom Energy</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, Tableau, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd1a549fc1388c4</t>
+          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>adswizz</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
+          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>BI Engineer , BI Center of Excellence</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Evolent</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
+          <t>Kafka Cluster Support Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
+          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
+          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
+          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
         </is>
       </c>
     </row>
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
+          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Networking Trainee</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BI Engineer , BI Center of Excellence</t>
+          <t>Senior Software Engineer, (.NET)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Evolent</t>
+          <t>Foundation Source</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, Scala, MySQL, CI/CD, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
+          <t>https://www.indeed.com/viewjob?jk=8d566d00eb2e403d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Kafka Cluster Support Engineer</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+          <t>RDS, Scala, PostgreSQL, DynamoDB, Splunk, CI/CD, Jenkins, Jenkins, SonarQube, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
+          <t>https://www.indeed.com/viewjob?jk=12e386150a46a2a5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>DATA SCIENTIST</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Tableau, Git, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
+          <t>https://www.indeed.com/viewjob?jk=c81ccc2c8f052915</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
+          <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Networking Trainee</t>
+          <t>Kafka Production Support Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, (.NET)</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Foundation Source</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, MySQL, CI/CD, Jenkins, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d566d00eb2e403d</t>
+          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DATA SCIENTIST</t>
+          <t>Commercial Operations BI Analyst</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Tableau, Git, Python, SQL, Scala</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c81ccc2c8f052915</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I</t>
+          <t>Business Intelligence Developer (Hybrid)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Westerra Credit Union</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, DynamoDB, Splunk, CI/CD, Jenkins, Jenkins, SonarQube, Git</t>
+          <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12e386150a46a2a5</t>
+          <t>https://www.indeed.com/viewjob?jk=ff473c63d82167e1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
+          <t>Security Consultant</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
+          <t>Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
+          <t>https://www.indeed.com/viewjob?jk=aa7381f71e38e6eb</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>AWS, Lambda, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3680,216 +3680,6 @@
         </is>
       </c>
       <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Kafka Production Support Engineer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Commercial Operations BI Analyst</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Colgate-Palmolive</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Piscataway, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Westerra Credit Union</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff473c63d82167e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Security Consultant</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa7381f71e38e6eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>SAS</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=38b2be41415df8a0</t>
         </is>

--- a/results/job_matches_2026-03-17.xlsx
+++ b/results/job_matches_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lyzr AI</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,77 +496,77 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a23265f32b23de3</t>
+          <t>https://www.indeed.com/viewjob?jk=b36bcd88655ec26b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer (Remote)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Flume, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36bcd88655ec26b</t>
+          <t>https://www.indeed.com/viewjob?jk=342faa6b5c9756a2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=342faa6b5c9756a2</t>
+          <t>https://www.indeed.com/viewjob?jk=4d6dc4080863d025</t>
         </is>
       </c>
     </row>
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d6dc4080863d025</t>
+          <t>https://www.indeed.com/viewjob?jk=9486e542e0314630</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9486e542e0314630</t>
+          <t>https://www.indeed.com/viewjob?jk=b271d311d5d546b6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b271d311d5d546b6</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d1545b725cacf9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d1545b725cacf9</t>
+          <t>https://www.indeed.com/viewjob?jk=6e62fa620ec25df7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Data Engineer with Python</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e62fa620ec25df7</t>
+          <t>https://www.indeed.com/viewjob?jk=c0b74cae84f6befa</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer with Python</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0b74cae84f6befa</t>
+          <t>https://www.indeed.com/viewjob?jk=9727641069e970c0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9727641069e970c0</t>
+          <t>https://www.indeed.com/viewjob?jk=8674e111f05b66a1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, IAM, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8674e111f05b66a1</t>
+          <t>https://www.indeed.com/viewjob?jk=c8e81977d38af04d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ETL Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CPI Security</t>
+          <t>Hays</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Carolina, PR, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e81977d38af04d</t>
+          <t>https://www.indeed.com/viewjob?jk=233a1a341ad0aa38</t>
         </is>
       </c>
     </row>
@@ -1168,25 +1168,25 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Participant Communication Services (PCS) Platform Architect - Virtual</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ed89084b43969d</t>
+          <t>https://www.indeed.com/viewjob?jk=02bd3db44eac42a0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02bd3db44eac42a0</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=407c52d9f78d8a4a</t>
+          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Software Engineer - TS/SCI with Polygraph</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Production Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Legion</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
+          <t>https://www.indeed.com/viewjob?jk=8bdd4694bf19ea44</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer - TS/SCI with Polygraph</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
+          <t>https://www.indeed.com/viewjob?jk=f1527cf38b699a4d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Production Engineer</t>
+          <t>Network Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, Spark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bdd4694bf19ea44</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7aa69b55de4760</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Network Operations Trainee</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1527cf38b699a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=88bda3516bc06812</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Network Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, Spark, Scala</t>
+          <t>Azure, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7aa69b55de4760</t>
+          <t>https://www.indeed.com/viewjob?jk=4181653d522a2852</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Network Operations Trainee</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88bda3516bc06812</t>
+          <t>https://www.indeed.com/viewjob?jk=4379abeabd8c87ca</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Kafka Operations Administrator</t>
+          <t>Kafka Data Replication Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, Splunk, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f208993ee2fdbe1c</t>
+          <t>https://www.indeed.com/viewjob?jk=4c99b3c52b9b8bc7</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Java Consultant</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4181653d522a2852</t>
+          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Backend Developer - .NET &amp; Azure</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Reidy</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4379abeabd8c87ca</t>
+          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Kafka Data Replication Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c99b3c52b9b8bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Java Consultant</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=239b1046f06d3d2f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Backend Developer - .NET &amp; Azure</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Reidy</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
+          <t>https://www.indeed.com/viewjob?jk=3a7f6dab575a97ad</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=d02a598ce56d257c</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=239b1046f06d3d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=0b64bf3747c350d3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>FundMate LLC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a7f6dab575a97ad</t>
+          <t>https://www.indeed.com/viewjob?jk=d833bbf779bc5e9f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, S3, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02a598ce56d257c</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab66e7fa68e90c6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b64bf3747c350d3</t>
+          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FundMate LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Jenkins</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d833bbf779bc5e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer Solution Design Focused</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>UnyBrands</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab66e7fa68e90c6</t>
+          <t>https://www.indeed.com/viewjob?jk=6d83c96f81842df2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Knightscope, Inc.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
+          <t>https://www.indeed.com/viewjob?jk=929003fb57aecac9</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Azure, Google Cloud Platform, PostgreSQL, MySQL, MongoDB, NoSQL, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
+          <t>https://www.indeed.com/viewjob?jk=f452a32fedc556a0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Solution Design Focused</t>
+          <t>Operations Analytics Data Scientist</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>UnyBrands</t>
+          <t>RadNet</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d83c96f81842df2</t>
+          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Kafka Administrator</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=929003fb57aecac9</t>
+          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>DBHDS - SQL Database Administrator</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Betis Group, Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, PostgreSQL, MySQL, MongoDB, NoSQL, Jenkins, Maven, Docker</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f452a32fedc556a0</t>
+          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Operations Analytics Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RadNet</t>
+          <t>Kimco Realty Corporation</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Kafka Administrator</t>
+          <t>Application Developer Sr II</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
+          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DBHDS - SQL Database Administrator</t>
+          <t>Application Developer Sr I</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Betis Group, Inc.</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
+          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Kimco Realty Corporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=016f2662bb776d79</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Application Developer Sr II</t>
+          <t>SQL DBA/ Data Engineer- AWS Migration</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
+          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Application Developer Sr I</t>
+          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Welltower, Inc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
+          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2416,29 +2416,29 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=016f2662bb776d79</t>
+          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SQL DBA/ Data Engineer- AWS Migration</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
+          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Welltower, Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a1692fa5839e7a</t>
+          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
+          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Excelsior University</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
+          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>adswizz</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,19 +2701,19 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
+          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2722,11 +2722,11 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
+          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Excelsior University</t>
+          <t>TeraWatt Infrastructure</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
+          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AI Industry 5.0 Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Bloom Energy</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, Tableau, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd1a549fc1388c4</t>
+          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>adswizz</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
+          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
+          <t>BI Engineer , BI Center of Excellence</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Evolent</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
+          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Kafka Cluster Support Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
+          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
+          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
+          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
+          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BI Engineer , BI Center of Excellence</t>
+          <t>Networking Trainee</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Evolent</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Kafka Cluster Support Engineer</t>
+          <t>Commercial Operations BI Analyst</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
+          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,14 +3226,14 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Kafka Production Support Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
+          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Networking Trainee</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, (.NET)</t>
+          <t>Business Intelligence Developer (Hybrid)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Foundation Source</t>
+          <t>Westerra Credit Union</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,367 +3321,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, MySQL, CI/CD, Jenkins, Docker, Jenkins, Git</t>
+          <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d566d00eb2e403d</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer I</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>RELX Group</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>RDS, Scala, PostgreSQL, DynamoDB, Splunk, CI/CD, Jenkins, Jenkins, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=12e386150a46a2a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>DATA SCIENTIST</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Dollar General</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Goodlettsville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Tableau, Git, Python, SQL, Scala</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c81ccc2c8f052915</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Bank of America</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Kafka</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Kafka Production Support Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Commercial Operations BI Analyst</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Colgate-Palmolive</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Piscataway, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Westerra Credit Union</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=ff473c63d82167e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Security Consultant</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa7381f71e38e6eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>SAS</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=38b2be41415df8a0</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-17.xlsx
+++ b/results/job_matches_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Software Engineer III - AWS Glue</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,24 +626,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b271d311d5d546b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c8436cd0c6787a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d1545b725cacf9</t>
+          <t>https://www.indeed.com/viewjob?jk=b271d311d5d546b6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e62fa620ec25df7</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d1545b725cacf9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer with Python</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0b74cae84f6befa</t>
+          <t>https://www.indeed.com/viewjob?jk=6e62fa620ec25df7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Data Engineer with Python</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9727641069e970c0</t>
+          <t>https://www.indeed.com/viewjob?jk=c0b74cae84f6befa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8674e111f05b66a1</t>
+          <t>https://www.indeed.com/viewjob?jk=9727641069e970c0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CPI Security</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e81977d38af04d</t>
+          <t>https://www.indeed.com/viewjob?jk=8674e111f05b66a1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ETL Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hays</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Carolina, PR, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, Kafka, Oracle</t>
+          <t>AWS, Lambda, S3, IAM, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=233a1a341ad0aa38</t>
+          <t>https://www.indeed.com/viewjob?jk=c8e81977d38af04d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kafka Data Streaming Consultant</t>
+          <t>ETL Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Hays</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Carolina, PR, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24db9c74d80b856c</t>
+          <t>https://www.indeed.com/viewjob?jk=233a1a341ad0aa38</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Kafka Data Streaming Consultant</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, ECS, RDS, Azure, Databricks, Cloud Storage</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e7128e441d147a</t>
+          <t>https://www.indeed.com/viewjob?jk=24db9c74d80b856c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, ECS, RDS, Azure, Databricks, Cloud Storage</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5861e377dbf3fbc8</t>
+          <t>https://www.indeed.com/viewjob?jk=33e7128e441d147a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd06ecb9103a776</t>
+          <t>https://www.indeed.com/viewjob?jk=5861e377dbf3fbc8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52c30ca213c085f</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd06ecb9103a776</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineer - AWS</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Purple Austyn Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=943257051095e0f6</t>
+          <t>https://www.indeed.com/viewjob?jk=c52c30ca213c085f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Big Data Engineer - AWS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>Purple Austyn Technologies</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8d99a7003ab349</t>
+          <t>https://www.indeed.com/viewjob?jk=943257051095e0f6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IAM Helpdesk Analyst</t>
+          <t>Software Engineer III: Machine Learning Platform</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, API Gateway, IAM, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5dd84afd435111</t>
+          <t>https://www.indeed.com/viewjob?jk=34e86f2f2a315595</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02bd3db44eac42a0</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8d99a7003ab349</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>IAM Helpdesk Analyst</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1217,11 +1217,11 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, API Gateway, IAM, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5dd84afd435111</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
+          <t>https://www.indeed.com/viewjob?jk=02bd3db44eac42a0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer - TS/SCI with Polygraph</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
+          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Production Engineer</t>
+          <t>Software Engineer - TS/SCI with Polygraph</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bdd4694bf19ea44</t>
+          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1357,11 +1357,11 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1527cf38b699a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Network Engineer</t>
+          <t>Senior Production Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Legion</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, Spark, Scala</t>
+          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7aa69b55de4760</t>
+          <t>https://www.indeed.com/viewjob?jk=8bdd4694bf19ea44</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Network Operations Trainee</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88bda3516bc06812</t>
+          <t>https://www.indeed.com/viewjob?jk=f1527cf38b699a4d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Network Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, Spark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4181653d522a2852</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7aa69b55de4760</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Network Operations Trainee</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4379abeabd8c87ca</t>
+          <t>https://www.indeed.com/viewjob?jk=88bda3516bc06812</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Kafka Data Replication Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c99b3c52b9b8bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Java Consultant</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
+          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Java Consultant</t>
+          <t>Backend Developer - .NET &amp; Azure</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Reidy</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Backend Developer - .NET &amp; Azure</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Reidy</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
+          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>Azure, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=4181653d522a2852</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=239b1046f06d3d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=4379abeabd8c87ca</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Kafka Data Replication Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Lambda, S3, ECS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a7f6dab575a97ad</t>
+          <t>https://www.indeed.com/viewjob?jk=4c99b3c52b9b8bc7</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02a598ce56d257c</t>
+          <t>https://www.indeed.com/viewjob?jk=239b1046f06d3d2f</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b64bf3747c350d3</t>
+          <t>https://www.indeed.com/viewjob?jk=3a7f6dab575a97ad</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FundMate LLC</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d833bbf779bc5e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=d02a598ce56d257c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab66e7fa68e90c6</t>
+          <t>https://www.indeed.com/viewjob?jk=0b64bf3747c350d3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FundMate LLC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
+          <t>https://www.indeed.com/viewjob?jk=d833bbf779bc5e9f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, S3, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab66e7fa68e90c6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Solution Design Focused</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>UnyBrands</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d83c96f81842df2</t>
+          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=929003fb57aecac9</t>
+          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Senior Data Engineer Solution Design Focused</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>UnyBrands</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, PostgreSQL, MySQL, MongoDB, NoSQL, Jenkins, Maven, Docker</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f452a32fedc556a0</t>
+          <t>https://www.indeed.com/viewjob?jk=6d83c96f81842df2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Operations Analytics Data Scientist</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RadNet</t>
+          <t>Knightscope, Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
+          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,14 +2106,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=929003fb57aecac9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kafka Administrator</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2127,11 +2127,11 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, PostgreSQL, MySQL, MongoDB, NoSQL, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
+          <t>https://www.indeed.com/viewjob?jk=f452a32fedc556a0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DBHDS - SQL Database Administrator</t>
+          <t>Operations Analytics Data Scientist</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Betis Group, Inc.</t>
+          <t>RadNet</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
+          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kafka Administrator</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Kimco Realty Corporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Application Developer Sr II</t>
+          <t>DBHDS - SQL Database Administrator</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Betis Group, Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
+          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Application Developer Sr I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Kimco Realty Corporation</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
+          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Application Developer Sr II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=016f2662bb776d79</t>
+          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SQL DBA/ Data Engineer- AWS Migration</t>
+          <t>Application Developer Sr I</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
+          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Welltower, Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,19 +2386,19 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
+          <t>https://www.indeed.com/viewjob?jk=016f2662bb776d79</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>SQL DBA/ Data Engineer- AWS Migration</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2416,29 +2416,29 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Welltower, Inc</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
+          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,14 +2526,14 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
+          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
         </is>
       </c>
     </row>
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
+          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Excelsior University</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
+          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>adswizz</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
+          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Excelsior University</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>SiriusXM</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
+          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>adswizz</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
+          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
+          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
+          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>TeraWatt Infrastructure</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BI Engineer , BI Center of Excellence</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Evolent</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,14 +2946,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
+          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Kafka Cluster Support Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
+          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
+          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>BI Engineer , BI Center of Excellence</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Evolent</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Kafka Cluster Support Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
+          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Networking Trainee</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Commercial Operations BI Analyst</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
+          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
+          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Networking Trainee</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Kafka Production Support Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
         </is>
       </c>
     </row>
@@ -3303,17 +3303,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer (Hybrid)</t>
+          <t>Kafka Production Support Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Westerra Credit Union</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,15 +3321,155 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Bank of America</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Kafka</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Commercial Operations BI Analyst</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Colgate-Palmolive</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Piscataway, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Business Intelligence Developer (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Westerra Credit Union</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
           <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ff473c63d82167e1</t>
         </is>

--- a/results/job_matches_2026-03-17.xlsx
+++ b/results/job_matches_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1203,7 +1203,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IAM Helpdesk Analyst</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1217,11 +1217,11 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, API Gateway, IAM, Scala</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5dd84afd435111</t>
+          <t>https://www.indeed.com/viewjob?jk=02bd3db44eac42a0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02bd3db44eac42a0</t>
+          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer - TS/SCI with Polygraph</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
+          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer - TS/SCI with Polygraph</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Senior Production Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Legion</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=8bdd4694bf19ea44</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Production Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bdd4694bf19ea44</t>
+          <t>https://www.indeed.com/viewjob?jk=f1527cf38b699a4d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Network Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, Spark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1527cf38b699a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7aa69b55de4760</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Network Engineer</t>
+          <t>Senior Software Engineer II - Backend - AI Search</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, Spark, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7aa69b55de4760</t>
+          <t>https://www.indeed.com/viewjob?jk=16388829699da902</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Network Operations Trainee</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88bda3516bc06812</t>
+          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Java Consultant</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
+          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Java Consultant</t>
+          <t>Backend Developer - .NET &amp; Azure</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Reidy</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Backend Developer - .NET &amp; Azure</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Reidy</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
+          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>Azure, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,14 +1651,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=4181653d522a2852</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,14 +1686,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4181653d522a2852</t>
+          <t>https://www.indeed.com/viewjob?jk=4379abeabd8c87ca</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Kafka Data Replication Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, S3, ECS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4379abeabd8c87ca</t>
+          <t>https://www.indeed.com/viewjob?jk=4c99b3c52b9b8bc7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Kafka Data Replication Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c99b3c52b9b8bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=239b1046f06d3d2f</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=239b1046f06d3d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=3a7f6dab575a97ad</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a7f6dab575a97ad</t>
+          <t>https://www.indeed.com/viewjob?jk=d02a598ce56d257c</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02a598ce56d257c</t>
+          <t>https://www.indeed.com/viewjob?jk=0b64bf3747c350d3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>FundMate LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b64bf3747c350d3</t>
+          <t>https://www.indeed.com/viewjob?jk=d833bbf779bc5e9f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FundMate LLC</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d833bbf779bc5e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab66e7fa68e90c6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab66e7fa68e90c6</t>
+          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
+          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Senior Data Engineer Solution Design Focused</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>UnyBrands</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
+          <t>https://www.indeed.com/viewjob?jk=6d83c96f81842df2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Solution Design Focused</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>UnyBrands</t>
+          <t>Knightscope, Inc.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt</t>
+          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d83c96f81842df2</t>
+          <t>https://www.indeed.com/viewjob?jk=929003fb57aecac9</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Operations Analytics Data Scientist</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>RadNet</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,14 +2106,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=929003fb57aecac9</t>
+          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Kafka Administrator</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2127,11 +2127,11 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, PostgreSQL, MySQL, MongoDB, NoSQL, Jenkins, Maven, Docker</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f452a32fedc556a0</t>
+          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Operations Analytics Data Scientist</t>
+          <t>DBHDS - SQL Database Administrator</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RadNet</t>
+          <t>Betis Group, Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kafka Administrator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kimco Realty Corporation</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
+          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DBHDS - SQL Database Administrator</t>
+          <t>Application Developer Sr II</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Betis Group, Inc.</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
+          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Application Developer Sr I</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Kimco Realty Corporation</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Application Developer Sr II</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
+          <t>https://www.indeed.com/viewjob?jk=016f2662bb776d79</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Application Developer Sr I</t>
+          <t>SQL DBA/ Data Engineer- AWS Migration</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
+          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Welltower, Inc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,19 +2386,19 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=016f2662bb776d79</t>
+          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SQL DBA/ Data Engineer- AWS Migration</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2416,29 +2416,29 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
+          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Welltower, Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,14 +2526,14 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
+          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
+          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
         </is>
       </c>
     </row>
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
+          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Excelsior University</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
+          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SiriusXM</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Excelsior University</t>
+          <t>adswizz</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
+          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SiriusXM</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
+          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>adswizz</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
+          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>TeraWatt Infrastructure</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
+          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
+          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
+          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>BI Engineer , BI Center of Excellence</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Evolent</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
+          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Kafka Cluster Support Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
+          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BI Engineer , BI Center of Excellence</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Evolent</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
+          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Kafka Cluster Support Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
+          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
+          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Networking Trainee</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Networking Trainee</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Kafka Production Support Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
+          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,14 +3296,14 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Kafka Production Support Engineer</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
+          <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
+          <t>Commercial Operations BI Analyst</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Business Intelligence Developer (Hybrid)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Westerra Credit Union</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3400,76 +3400,6 @@
         </is>
       </c>
       <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Commercial Operations BI Analyst</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Colgate-Palmolive</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Piscataway, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Westerra Credit Union</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ff473c63d82167e1</t>
         </is>

--- a/results/job_matches_2026-03-17.xlsx
+++ b/results/job_matches_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Glue</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tapouts</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Venice, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c8436cd0c6787a</t>
+          <t>https://www.indeed.com/viewjob?jk=bcb6f48928a08bed</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Software Engineer III - AWS Glue</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,24 +661,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b271d311d5d546b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c8436cd0c6787a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d1545b725cacf9</t>
+          <t>https://www.indeed.com/viewjob?jk=b271d311d5d546b6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e62fa620ec25df7</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d1545b725cacf9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer with Python</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0b74cae84f6befa</t>
+          <t>https://www.indeed.com/viewjob?jk=6e62fa620ec25df7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Data Engineer with Python</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9727641069e970c0</t>
+          <t>https://www.indeed.com/viewjob?jk=c0b74cae84f6befa</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8674e111f05b66a1</t>
+          <t>https://www.indeed.com/viewjob?jk=9727641069e970c0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CPI Security</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e81977d38af04d</t>
+          <t>https://www.indeed.com/viewjob?jk=8674e111f05b66a1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ETL Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hays</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Carolina, PR, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, Kafka, Oracle</t>
+          <t>AWS, Lambda, S3, IAM, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=233a1a341ad0aa38</t>
+          <t>https://www.indeed.com/viewjob?jk=c8e81977d38af04d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kafka Data Streaming Consultant</t>
+          <t>ETL Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Hays</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Carolina, PR, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24db9c74d80b856c</t>
+          <t>https://www.indeed.com/viewjob?jk=233a1a341ad0aa38</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Kafka Data Streaming Consultant</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, ECS, RDS, Azure, Databricks, Cloud Storage</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e7128e441d147a</t>
+          <t>https://www.indeed.com/viewjob?jk=24db9c74d80b856c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5861e377dbf3fbc8</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd06ecb9103a776</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, ECS, RDS, Azure, Databricks, Cloud Storage</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd06ecb9103a776</t>
+          <t>https://www.indeed.com/viewjob?jk=33e7128e441d147a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52c30ca213c085f</t>
+          <t>https://www.indeed.com/viewjob?jk=5861e377dbf3fbc8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineer - AWS</t>
+          <t>Software Engineer III: Machine Learning Platform</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Purple Austyn Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=943257051095e0f6</t>
+          <t>https://www.indeed.com/viewjob?jk=34e86f2f2a315595</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer III: Machine Learning Platform</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34e86f2f2a315595</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8d99a7003ab349</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8d99a7003ab349</t>
+          <t>https://www.indeed.com/viewjob?jk=c52c30ca213c085f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Senior Big Data Engineer - AWS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Purple Austyn Technologies</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02bd3db44eac42a0</t>
+          <t>https://www.indeed.com/viewjob?jk=943257051095e0f6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
+          <t>https://www.indeed.com/viewjob?jk=ee3c21dbe995c8b9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer - TS/SCI with Polygraph</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
+          <t>https://www.indeed.com/viewjob?jk=02bd3db44eac42a0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,42 +1326,42 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Production Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bdd4694bf19ea44</t>
+          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Software Engineer - TS/SCI with Polygraph</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1527cf38b699a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Network Engineer</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1427,11 +1427,11 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, Spark, Scala</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7aa69b55de4760</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Backend - AI Search</t>
+          <t>Senior Production Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Legion</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16388829699da902</t>
+          <t>https://www.indeed.com/viewjob?jk=8bdd4694bf19ea44</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
+          <t>https://www.indeed.com/viewjob?jk=f1527cf38b699a4d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Java Consultant</t>
+          <t>Network Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, Spark, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7aa69b55de4760</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Backend Developer - .NET &amp; Azure</t>
+          <t>Senior Software Engineer II - Backend - AI Search</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Reidy</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
+          <t>https://www.indeed.com/viewjob?jk=16388829699da902</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Cloud Identity Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=f892a7ff9f3b3673</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,14 +1651,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4181653d522a2852</t>
+          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Java Consultant</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4379abeabd8c87ca</t>
+          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Kafka Data Replication Engineer</t>
+          <t>Backend Developer - .NET &amp; Azure</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Reidy</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c99b3c52b9b8bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=239b1046f06d3d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>Azure, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a7f6dab575a97ad</t>
+          <t>https://www.indeed.com/viewjob?jk=4181653d522a2852</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02a598ce56d257c</t>
+          <t>https://www.indeed.com/viewjob?jk=4379abeabd8c87ca</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Kafka Data Replication Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Lambda, S3, ECS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b64bf3747c350d3</t>
+          <t>https://www.indeed.com/viewjob?jk=4c99b3c52b9b8bc7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FundMate LLC</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d833bbf779bc5e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=239b1046f06d3d2f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab66e7fa68e90c6</t>
+          <t>https://www.indeed.com/viewjob?jk=3a7f6dab575a97ad</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
+          <t>https://www.indeed.com/viewjob?jk=d02a598ce56d257c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
+          <t>https://www.indeed.com/viewjob?jk=0b64bf3747c350d3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Solution Design Focused</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>UnyBrands</t>
+          <t>FundMate LLC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt</t>
+          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d83c96f81842df2</t>
+          <t>https://www.indeed.com/viewjob?jk=d833bbf779bc5e9f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=929003fb57aecac9</t>
+          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Operations Analytics Data Scientist</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RadNet</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kafka Administrator</t>
+          <t>Senior Data Engineer Solution Design Focused</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>UnyBrands</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
+          <t>https://www.indeed.com/viewjob?jk=6d83c96f81842df2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DBHDS - SQL Database Administrator</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Betis Group, Inc.</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, S3, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab66e7fa68e90c6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Kimco Realty Corporation</t>
+          <t>Knightscope, Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=929003fb57aecac9</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Application Developer Sr II</t>
+          <t>Vector Database Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
+          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Application Developer Sr I</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
+          <t>https://www.indeed.com/viewjob?jk=d78a7ea53a7fb5c5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>DBHDS - SQL Database Administrator</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Betis Group, Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=016f2662bb776d79</t>
+          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SQL DBA/ Data Engineer- AWS Migration</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Kimco Realty Corporation</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
+          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
+          <t>Application Developer Sr II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Welltower, Inc</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
+          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Application Developer Sr I</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,24 +2411,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
+          <t>https://www.indeed.com/viewjob?jk=016f2662bb776d79</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SQL DBA/ Data Engineer- AWS Migration</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
+          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Welltower, Inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
+          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Operations Analytics Data Scientist</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RadNet</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
+          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Kafka Administrator</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Excelsior University</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SiriusXM</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
+          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>adswizz</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,19 +2736,19 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
+          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2757,11 +2757,11 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,67 +2771,67 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
+          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
+          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Excelsior University</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
+          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
         </is>
       </c>
     </row>
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
+          <t>https://www.indeed.com/viewjob?jk=703ef93955ad68ff</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BI Engineer , BI Center of Excellence</t>
+          <t>Networking Trainee</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Evolent</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
+          <t>https://www.indeed.com/viewjob?jk=852483a8d2e6f7e3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Kafka Cluster Support Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SiriusXM</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
+          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TeraWatt Infrastructure</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>adswizz</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
+          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Networking Trainee</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
+          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Kafka Production Support Engineer</t>
+          <t>BI Engineer , BI Center of Excellence</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Evolent</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
+          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
+          <t>Kafka Cluster Support Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,14 +3296,14 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
+          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
+          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Commercial Operations BI Analyst</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
+          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer (Hybrid)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Westerra Credit Union</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,15 +3391,295 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Networking Trainee</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>HealthEdge Software, Inc.</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Kafka Production Support Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Bank of America</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Kafka</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Commercial Operations BI Analyst</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Colgate-Palmolive</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Piscataway, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Business Intelligence Developer (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Westerra Credit Union</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
           <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ff473c63d82167e1</t>
         </is>

--- a/results/job_matches_2026-03-17.xlsx
+++ b/results/job_matches_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, ECS, RDS, Azure, Databricks, Cloud Storage</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd06ecb9103a776</t>
+          <t>https://www.indeed.com/viewjob?jk=33e7128e441d147a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, ECS, RDS, Azure, Databricks, Cloud Storage</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e7128e441d147a</t>
+          <t>https://www.indeed.com/viewjob?jk=5861e377dbf3fbc8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5861e377dbf3fbc8</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd06ecb9103a776</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer III: Machine Learning Platform</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34e86f2f2a315595</t>
+          <t>https://www.indeed.com/viewjob?jk=c52c30ca213c085f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Software Engineer III: Machine Learning Platform</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8d99a7003ab349</t>
+          <t>https://www.indeed.com/viewjob?jk=34e86f2f2a315595</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,59 +1196,59 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52c30ca213c085f</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8d99a7003ab349</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineer - AWS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Purple Austyn Technologies</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=943257051095e0f6</t>
+          <t>https://www.indeed.com/viewjob?jk=ee3c21dbe995c8b9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee3c21dbe995c8b9</t>
+          <t>https://www.indeed.com/viewjob?jk=02bd3db44eac42a0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02bd3db44eac42a0</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
+          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer - TS/SCI with Polygraph</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
+          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer - TS/SCI with Polygraph</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Senior Production Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Legion</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=8bdd4694bf19ea44</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Production Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bdd4694bf19ea44</t>
+          <t>https://www.indeed.com/viewjob?jk=f1527cf38b699a4d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Network Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, Spark, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1527cf38b699a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7aa69b55de4760</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Network Engineer</t>
+          <t>Cloud Identity Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, Spark, Scala</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7aa69b55de4760</t>
+          <t>https://www.indeed.com/viewjob?jk=f892a7ff9f3b3673</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f892a7ff9f3b3673</t>
+          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Java Consultant</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
+          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Java Consultant</t>
+          <t>Backend Developer - .NET &amp; Azure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Reidy</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Backend Developer - .NET &amp; Azure</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Reidy</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
+          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>Azure, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,14 +1756,14 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=4181653d522a2852</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,14 +1791,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4181653d522a2852</t>
+          <t>https://www.indeed.com/viewjob?jk=4379abeabd8c87ca</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Kafka Data Replication Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, S3, ECS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4379abeabd8c87ca</t>
+          <t>https://www.indeed.com/viewjob?jk=4c99b3c52b9b8bc7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Kafka Data Replication Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c99b3c52b9b8bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=239b1046f06d3d2f</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=239b1046f06d3d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=3a7f6dab575a97ad</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a7f6dab575a97ad</t>
+          <t>https://www.indeed.com/viewjob?jk=d02a598ce56d257c</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02a598ce56d257c</t>
+          <t>https://www.indeed.com/viewjob?jk=0b64bf3747c350d3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>FundMate LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b64bf3747c350d3</t>
+          <t>https://www.indeed.com/viewjob?jk=d833bbf779bc5e9f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FundMate LLC</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d833bbf779bc5e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab66e7fa68e90c6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Sr. Data Engineer – Ontology &amp; Semantic Modeling</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SoundThinking</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
+          <t>https://www.indeed.com/viewjob?jk=e92d0315202204b9</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
+          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Solution Design Focused</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>UnyBrands</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d83c96f81842df2</t>
+          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Knightscope, Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab66e7fa68e90c6</t>
+          <t>https://www.indeed.com/viewjob?jk=929003fb57aecac9</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Operations Analytics Data Scientist</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>RadNet</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,14 +2211,14 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=929003fb57aecac9</t>
+          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Vector Database Engineer</t>
+          <t>Kafka Administrator</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2236,24 +2236,24 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
+          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Vector Database Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d78a7ea53a7fb5c5</t>
+          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Operations Analytics Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RadNet</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Kafka Administrator</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
+          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,14 +2666,14 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
+          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
+          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
+          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Excelsior University</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SiriusXM</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
+          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>adswizz</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Excelsior University</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
+          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
         </is>
       </c>
     </row>
@@ -2918,17 +2918,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TeraWatt Infrastructure</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=703ef93955ad68ff</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Networking Trainee</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=852483a8d2e6f7e3</t>
+          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SiriusXM</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
+          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
+          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>BI Engineer , BI Center of Excellence</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>adswizz</t>
+          <t>Evolent</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
+          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kafka Cluster Support Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
+          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
+          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
+          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BI Engineer , BI Center of Excellence</t>
+          <t>Networking Trainee</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Evolent</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Kafka Cluster Support Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,14 +3331,14 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
+          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Kafka Production Support Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Commercial Operations BI Analyst</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Networking Trainee</t>
+          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
+          <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Business Intelligence Developer (Hybrid)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Westerra Credit Union</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
+          <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3505,181 +3505,6 @@
         </is>
       </c>
       <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Kafka Production Support Engineer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Bank of America</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Kafka</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Commercial Operations BI Analyst</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Colgate-Palmolive</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Piscataway, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Westerra Credit Union</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ff473c63d82167e1</t>
         </is>

--- a/results/job_matches_2026-03-17.xlsx
+++ b/results/job_matches_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,70 +503,70 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>National Rural Water Association</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Duncan, OK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, SQL Server</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=342faa6b5c9756a2</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf4aa616b7efc0f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d6dc4080863d025</t>
+          <t>https://www.indeed.com/viewjob?jk=342faa6b5c9756a2</t>
         </is>
       </c>
     </row>
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9486e542e0314630</t>
+          <t>https://www.indeed.com/viewjob?jk=4d6dc4080863d025</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tapouts</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Venice, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcb6f48928a08bed</t>
+          <t>https://www.indeed.com/viewjob?jk=9486e542e0314630</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Glue</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tapouts</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Venice, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c8436cd0c6787a</t>
+          <t>https://www.indeed.com/viewjob?jk=bcb6f48928a08bed</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Software Engineer III - AWS Glue</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,24 +696,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b271d311d5d546b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c8436cd0c6787a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d1545b725cacf9</t>
+          <t>https://www.indeed.com/viewjob?jk=b271d311d5d546b6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e62fa620ec25df7</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d1545b725cacf9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer with Python</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0b74cae84f6befa</t>
+          <t>https://www.indeed.com/viewjob?jk=6e62fa620ec25df7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Data Engineer with Python</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9727641069e970c0</t>
+          <t>https://www.indeed.com/viewjob?jk=c0b74cae84f6befa</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8674e111f05b66a1</t>
+          <t>https://www.indeed.com/viewjob?jk=9727641069e970c0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CPI Security</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e81977d38af04d</t>
+          <t>https://www.indeed.com/viewjob?jk=8674e111f05b66a1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ETL Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hays</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Carolina, PR, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, Kafka, Oracle</t>
+          <t>AWS, Lambda, S3, IAM, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=233a1a341ad0aa38</t>
+          <t>https://www.indeed.com/viewjob?jk=c8e81977d38af04d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kafka Data Streaming Consultant</t>
+          <t>ETL Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Hays</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Carolina, PR, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24db9c74d80b856c</t>
+          <t>https://www.indeed.com/viewjob?jk=233a1a341ad0aa38</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Kafka Data Streaming Consultant</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, ECS, RDS, Azure, Databricks, Cloud Storage</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e7128e441d147a</t>
+          <t>https://www.indeed.com/viewjob?jk=24db9c74d80b856c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, ECS, RDS, Azure, Databricks, Cloud Storage</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5861e377dbf3fbc8</t>
+          <t>https://www.indeed.com/viewjob?jk=33e7128e441d147a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd06ecb9103a776</t>
+          <t>https://www.indeed.com/viewjob?jk=5861e377dbf3fbc8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1112,11 +1112,11 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52c30ca213c085f</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd06ecb9103a776</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer III: Machine Learning Platform</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34e86f2f2a315595</t>
+          <t>https://www.indeed.com/viewjob?jk=c52c30ca213c085f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Software Engineer III: Machine Learning Platform</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,69 +1186,69 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8d99a7003ab349</t>
+          <t>https://www.indeed.com/viewjob?jk=34e86f2f2a315595</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee3c21dbe995c8b9</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8d99a7003ab349</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02bd3db44eac42a0</t>
+          <t>https://www.indeed.com/viewjob?jk=ee3c21dbe995c8b9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
+          <t>https://www.indeed.com/viewjob?jk=02bd3db44eac42a0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer - TS/SCI with Polygraph</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
+          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Software Engineer - TS/SCI with Polygraph</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Production Engineer</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bdd4694bf19ea44</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Radiant Digital</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1527cf38b699a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=72e4768c31a35e7d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Network Engineer</t>
+          <t>Senior Production Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Legion</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, Spark, Scala</t>
+          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7aa69b55de4760</t>
+          <t>https://www.indeed.com/viewjob?jk=8bdd4694bf19ea44</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f892a7ff9f3b3673</t>
+          <t>https://www.indeed.com/viewjob?jk=f1527cf38b699a4d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Backend - AI Search</t>
+          <t>Network Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, Spark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16388829699da902</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7aa69b55de4760</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Software Engineer II - Backend - AI Search</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,14 +1616,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
+          <t>https://www.indeed.com/viewjob?jk=16388829699da902</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Java Consultant</t>
+          <t>Cloud Identity Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=f892a7ff9f3b3673</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Backend Developer - .NET &amp; Azure</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Reidy</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
+          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Java Consultant</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Backend Developer - .NET &amp; Azure</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Reidy</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4181653d522a2852</t>
+          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,14 +1791,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4379abeabd8c87ca</t>
+          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Kafka Data Replication Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>Azure, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c99b3c52b9b8bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=4181653d522a2852</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=239b1046f06d3d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=4379abeabd8c87ca</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Kafka Data Replication Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Lambda, S3, ECS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a7f6dab575a97ad</t>
+          <t>https://www.indeed.com/viewjob?jk=4c99b3c52b9b8bc7</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02a598ce56d257c</t>
+          <t>https://www.indeed.com/viewjob?jk=239b1046f06d3d2f</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b64bf3747c350d3</t>
+          <t>https://www.indeed.com/viewjob?jk=3a7f6dab575a97ad</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FundMate LLC</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d833bbf779bc5e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=d02a598ce56d257c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,59 +2036,59 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab66e7fa68e90c6</t>
+          <t>https://www.indeed.com/viewjob?jk=0b64bf3747c350d3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer – Ontology &amp; Semantic Modeling</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SoundThinking</t>
+          <t>FundMate LLC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e92d0315202204b9</t>
+          <t>https://www.indeed.com/viewjob?jk=d833bbf779bc5e9f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, S3, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab66e7fa68e90c6</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
+          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=929003fb57aecac9</t>
+          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Operations Analytics Data Scientist</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RadNet</t>
+          <t>Knightscope, Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
+          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=929003fb57aecac9</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Kafka Administrator</t>
+          <t>Operations Analytics Data Scientist</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RadNet</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,14 +2246,14 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
+          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Vector Database Engineer</t>
+          <t>Kafka Administrator</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
+          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DBHDS - SQL Database Administrator</t>
+          <t>Vector Database Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Betis Group, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2311,29 +2311,29 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
+          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DBHDS - SQL Database Administrator</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Kimco Realty Corporation</t>
+          <t>Betis Group, Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Application Developer Sr II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Kimco Realty Corporation</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,14 +2386,14 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
+          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Application Developer Sr I</t>
+          <t>Application Developer Sr II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
+          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Application Developer Sr I</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=016f2662bb776d79</t>
+          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SQL DBA/ Data Engineer- AWS Migration</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
+          <t>https://www.indeed.com/viewjob?jk=016f2662bb776d79</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
+          <t>SQL DBA/ Data Engineer- AWS Migration</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Welltower, Inc</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
+          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Welltower, Inc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
+          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
         </is>
       </c>
     </row>
@@ -2573,12 +2573,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bridgeton, MO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, SQS, SNS, RDS, Scala, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
+          <t>https://www.indeed.com/viewjob?jk=ef17b59d1b779ca6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SiriusXM</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
+          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>adswizz</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Excelsior University</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
+          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SiriusXM</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>adswizz</t>
+          <t>TeraWatt Infrastructure</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
         </is>
       </c>
     </row>
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
+          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
+          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>BI Engineer , BI Center of Excellence</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Evolent</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
+          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Kafka Cluster Support Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
+          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
+          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BI Engineer , BI Center of Excellence</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Evolent</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
+          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Kafka Cluster Support Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
+          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Networking Trainee</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>AWS, Kinesis, SQS, RDS, Scala, Kafka, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=8ba2a4b5e0580ed9</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Networking Trainee</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Kafka Production Support Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
+          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,14 +3331,14 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Kafka Production Support Engineer</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
+          <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
         </is>
       </c>
     </row>
@@ -3408,12 +3408,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
+          <t>Business Intelligence Developer (Hybrid)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Westerra Credit Union</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
+          <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3435,76 +3435,6 @@
         </is>
       </c>
       <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Kafka</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Westerra Credit Union</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ff473c63d82167e1</t>
         </is>

--- a/results/job_matches_2026-03-17.xlsx
+++ b/results/job_matches_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,70 +503,70 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>National Rural Water Association</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Duncan, OK, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcf4aa616b7efc0f</t>
+          <t>https://www.indeed.com/viewjob?jk=342faa6b5c9756a2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=342faa6b5c9756a2</t>
+          <t>https://www.indeed.com/viewjob?jk=4d6dc4080863d025</t>
         </is>
       </c>
     </row>
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d6dc4080863d025</t>
+          <t>https://www.indeed.com/viewjob?jk=9486e542e0314630</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tapouts</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Venice, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9486e542e0314630</t>
+          <t>https://www.indeed.com/viewjob?jk=bcb6f48928a08bed</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - AWS Glue</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tapouts</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Venice, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcb6f48928a08bed</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c8436cd0c6787a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Glue</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,24 +696,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
+          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c8436cd0c6787a</t>
+          <t>https://www.indeed.com/viewjob?jk=b271d311d5d546b6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b271d311d5d546b6</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d1545b725cacf9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d1545b725cacf9</t>
+          <t>https://www.indeed.com/viewjob?jk=6e62fa620ec25df7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ARCHKEY SOLUTIONS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fenton, MO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e62fa620ec25df7</t>
+          <t>https://www.indeed.com/viewjob?jk=ecdbaaed7feccfa0</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
+          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer - TS/SCI with Polygraph</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
+          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer - TS/SCI with Polygraph</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Backend - AI Search</t>
+          <t>Smart Factory Data Engineering Architect (AWS/manufacturing)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Reignmarkcs</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Spark, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16388829699da902</t>
+          <t>https://www.indeed.com/viewjob?jk=7331096c97ad5651</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>Senior Software Engineer II - Backend - AI Search</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f892a7ff9f3b3673</t>
+          <t>https://www.indeed.com/viewjob?jk=16388829699da902</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
+          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=929003fb57aecac9</t>
+          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Operations Analytics Data Scientist</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RadNet</t>
+          <t>Knightscope, Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
+          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=929003fb57aecac9</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Kafka Administrator</t>
+          <t>Operations Analytics Data Scientist</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RadNet</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,14 +2281,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
+          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Vector Database Engineer</t>
+          <t>Kafka Administrator</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
+          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DBHDS - SQL Database Administrator</t>
+          <t>Vector Database Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Betis Group, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2346,29 +2346,29 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
+          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DBHDS - SQL Database Administrator</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Kimco Realty Corporation</t>
+          <t>Betis Group, Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Application Developer Sr II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Kimco Realty Corporation</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,14 +2421,14 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
+          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Application Developer Sr I</t>
+          <t>Application Developer Sr II</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
+          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Application Developer Sr I</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=016f2662bb776d79</t>
+          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SQL DBA/ Data Engineer- AWS Migration</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
+          <t>https://www.indeed.com/viewjob?jk=016f2662bb776d79</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Welltower, Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bridgeton, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,42 +2586,42 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, RDS, Scala, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef17b59d1b779ca6</t>
+          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SiriusXM</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
+          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>adswizz</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SiriusXM</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
+          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>adswizz</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
+          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TeraWatt Infrastructure</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
+          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
+          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
+          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>BI Engineer , BI Center of Excellence</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Evolent</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
+          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BI Engineer , BI Center of Excellence</t>
+          <t>Kafka Cluster Support Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Evolent</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
+          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Kafka Cluster Support Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
+          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
+          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Networking Trainee</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Networking Trainee</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Scala, Kafka, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ba2a4b5e0580ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Kafka Production Support Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
+          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,14 +3261,14 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Kafka Production Support Engineer</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
+          <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
+          <t>Commercial Operations BI Analyst</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Business Intelligence Developer (Hybrid)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Westerra Credit Union</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3365,76 +3365,6 @@
         </is>
       </c>
       <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Commercial Operations BI Analyst</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Colgate-Palmolive</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Piscataway, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Westerra Credit Union</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ff473c63d82167e1</t>
         </is>

--- a/results/job_matches_2026-03-17.xlsx
+++ b/results/job_matches_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,87 +538,87 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tapouts</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Venice, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d6dc4080863d025</t>
+          <t>https://www.indeed.com/viewjob?jk=bcb6f48928a08bed</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Software Engineer III - AWS Glue</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9486e542e0314630</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c8436cd0c6787a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tapouts</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Venice, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcb6f48928a08bed</t>
+          <t>https://www.indeed.com/viewjob?jk=b271d311d5d546b6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Glue</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>ARCHKEY SOLUTIONS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Fenton, MO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c8436cd0c6787a</t>
+          <t>https://www.indeed.com/viewjob?jk=ecdbaaed7feccfa0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Data Engineer with Python</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b271d311d5d546b6</t>
+          <t>https://www.indeed.com/viewjob?jk=c0b74cae84f6befa</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d1545b725cacf9</t>
+          <t>https://www.indeed.com/viewjob?jk=c8e81977d38af04d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>ETL Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Hays</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Carolina, PR, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e62fa620ec25df7</t>
+          <t>https://www.indeed.com/viewjob?jk=233a1a341ad0aa38</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ARCHKEY SOLUTIONS</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fenton, MO, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, ECS, RDS, Azure, Databricks, Cloud Storage</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecdbaaed7feccfa0</t>
+          <t>https://www.indeed.com/viewjob?jk=33e7128e441d147a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer with Python</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0b74cae84f6befa</t>
+          <t>https://www.indeed.com/viewjob?jk=5861e377dbf3fbc8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Software Engineer III: Machine Learning Platform</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9727641069e970c0</t>
+          <t>https://www.indeed.com/viewjob?jk=34e86f2f2a315595</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,312 +916,312 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8674e111f05b66a1</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8d99a7003ab349</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CPI Security</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e81977d38af04d</t>
+          <t>https://www.indeed.com/viewjob?jk=ee3c21dbe995c8b9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ETL Data Engineer</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hays</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Carolina, PR, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, Kafka, Oracle</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=233a1a341ad0aa38</t>
+          <t>https://www.indeed.com/viewjob?jk=29610b7eba9cc4cb</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kafka Data Streaming Consultant</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24db9c74d80b856c</t>
+          <t>https://www.indeed.com/viewjob?jk=693bc93cfe95e968</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, ECS, RDS, Azure, Databricks, Cloud Storage</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e7128e441d147a</t>
+          <t>https://www.indeed.com/viewjob?jk=fafa6085d07ec220</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5861e377dbf3fbc8</t>
+          <t>https://www.indeed.com/viewjob?jk=71120e321dbd18c4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd06ecb9103a776</t>
+          <t>https://www.indeed.com/viewjob?jk=be687a9701ed10cb</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Systems Administrator</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HH Brown Shoe Company</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Martinsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52c30ca213c085f</t>
+          <t>https://www.indeed.com/viewjob?jk=0bca63db22516c1c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer III: Machine Learning Platform</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34e86f2f2a315595</t>
+          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Software Engineer - TS/SCI with Polygraph</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8d99a7003ab349</t>
+          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,137 +1266,137 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee3c21dbe995c8b9</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Healthix</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02bd3db44eac42a0</t>
+          <t>https://www.indeed.com/viewjob?jk=b51729f31816ec17</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Radiant Digital</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
+          <t>https://www.indeed.com/viewjob?jk=72e4768c31a35e7d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer - TS/SCI with Polygraph</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
+          <t>https://www.indeed.com/viewjob?jk=4efec6d9008a5b85</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Senior Software Engineer II - Backend - AI Search</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,59 +1406,59 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=16388829699da902</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
+          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Java Consultant</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Radiant Digital</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72e4768c31a35e7d</t>
+          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Production Engineer</t>
+          <t>Backend Developer - .NET &amp; Azure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>Reidy</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bdd4694bf19ea44</t>
+          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1527cf38b699a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Network Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, Spark, Scala</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7aa69b55de4760</t>
+          <t>https://www.indeed.com/viewjob?jk=239b1046f06d3d2f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Smart Factory Data Engineering Architect (AWS/manufacturing)</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Reignmarkcs</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Databricks, Spark, Data Modeling</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7331096c97ad5651</t>
+          <t>https://www.indeed.com/viewjob?jk=3a7f6dab575a97ad</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Backend - AI Search</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16388829699da902</t>
+          <t>https://www.indeed.com/viewjob?jk=d02a598ce56d257c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
+          <t>https://www.indeed.com/viewjob?jk=0b64bf3747c350d3</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Java Consultant</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FundMate LLC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=d833bbf779bc5e9f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Backend Developer - .NET &amp; Azure</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Reidy</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab66e7fa68e90c6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4181653d522a2852</t>
+          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4379abeabd8c87ca</t>
+          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Kafka Data Replication Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Knightscope, Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,67 +1896,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c99b3c52b9b8bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=929003fb57aecac9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=239b1046f06d3d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Operations Analytics Data Scientist</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>RadNet</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,67 +1966,67 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a7f6dab575a97ad</t>
+          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Vector Database Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02a598ce56d257c</t>
+          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>DBHDS - SQL Database Administrator</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Betis Group, Inc.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b64bf3747c350d3</t>
+          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FundMate LLC</t>
+          <t>Kimco Realty Corporation</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d833bbf779bc5e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Application Developer Sr II</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,102 +2106,102 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab66e7fa68e90c6</t>
+          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Application Developer Sr I</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
+          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
+          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>SiriusXM</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=929003fb57aecac9</t>
+          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Operations Analytics Data Scientist</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RadNet</t>
+          <t>adswizz</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Kafka Administrator</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
+          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Vector Database Engineer</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,67 +2351,67 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
+          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DBHDS - SQL Database Administrator</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Betis Group, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Kimco Realty Corporation</t>
+          <t>TeraWatt Infrastructure</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Application Developer Sr II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
+          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Application Developer Sr I</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
+          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=016f2662bb776d79</t>
+          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>BI Engineer , BI Center of Excellence</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Evolent</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
+          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SiriusXM</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>adswizz</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
+          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Business Intelligence Developer (Hybrid)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Westerra Credit Union</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=ff473c63d82167e1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Commercial Operations BI Analyst</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,647 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>AWS Network Engineer</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>TeraWatt Infrastructure</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>VeeRteq Solutions Inc.</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>AWS Network Engineer</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>AMH</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Draper, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>BI Engineer , BI Center of Excellence</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Evolent</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Kafka Cluster Support Engineer</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Azure Network Engineer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>AWS Network Engineer</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>AWS Network Engineer</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Networking Trainee</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>HealthEdge Software, Inc.</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Kafka Production Support Engineer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Bank of America</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Kafka</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Commercial Operations BI Analyst</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Colgate-Palmolive</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Piscataway, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Westerra Credit Union</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff473c63d82167e1</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-17.xlsx
+++ b/results/job_matches_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tapouts</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Venice, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcb6f48928a08bed</t>
+          <t>https://www.indeed.com/viewjob?jk=5be2803455ebf096</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Glue</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tapouts</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Venice, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c8436cd0c6787a</t>
+          <t>https://www.indeed.com/viewjob?jk=bcb6f48928a08bed</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Software Engineer III - AWS Glue</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b271d311d5d546b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c8436cd0c6787a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Sr Agile Developer - Datamart</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ARCHKEY SOLUTIONS</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fenton, MO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,77 +661,77 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecdbaaed7feccfa0</t>
+          <t>https://www.indeed.com/viewjob?jk=8b0a1eacc51b9571</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer with Python</t>
+          <t>Sr Agile Developer - Datamart</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0b74cae84f6befa</t>
+          <t>https://www.indeed.com/viewjob?jk=15708f0e06d200c6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CPI Security</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e81977d38af04d</t>
+          <t>https://www.indeed.com/viewjob?jk=b271d311d5d546b6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ETL Data Engineer</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hays</t>
+          <t>ARCHKEY SOLUTIONS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Carolina, PR, US USA</t>
+          <t>Fenton, MO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,102 +776,102 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=233a1a341ad0aa38</t>
+          <t>https://www.indeed.com/viewjob?jk=ecdbaaed7feccfa0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, ECS, RDS, Azure, Databricks, Cloud Storage</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e7128e441d147a</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd7396ffb6ba90c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior DevOps Cloud Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5861e377dbf3fbc8</t>
+          <t>https://www.indeed.com/viewjob?jk=0f9a6991656b7b52</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer III: Machine Learning Platform</t>
+          <t>Azure ETL Developer with Advance Power BI Experience - Public transportation domain experience</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Syncreon Consulting</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34e86f2f2a315595</t>
+          <t>https://www.indeed.com/viewjob?jk=4c016dae6a0a4e49</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Cloud-Native MLOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8d99a7003ab349</t>
+          <t>https://www.indeed.com/viewjob?jk=a456d96d929a416c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kafka API Gateway Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee3c21dbe995c8b9</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5ee5a6cd78dc32</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29610b7eba9cc4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=8fb3549614f234b2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, IAM, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693bc93cfe95e968</t>
+          <t>https://www.indeed.com/viewjob?jk=c8e81977d38af04d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Kafka Spark Streaming Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,207 +1056,207 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fafa6085d07ec220</t>
+          <t>https://www.indeed.com/viewjob?jk=96cb2fd809795c0f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>ETL Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Hays</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Carolina, PR, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71120e321dbd18c4</t>
+          <t>https://www.indeed.com/viewjob?jk=233a1a341ad0aa38</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, ECS, RDS, Azure, Databricks, Cloud Storage</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be687a9701ed10cb</t>
+          <t>https://www.indeed.com/viewjob?jk=33e7128e441d147a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Systems Administrator</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HH Brown Shoe Company</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Martinsburg, PA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bca63db22516c1c</t>
+          <t>https://www.indeed.com/viewjob?jk=5861e377dbf3fbc8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Flask Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
+          <t>https://www.indeed.com/viewjob?jk=7e317c65dceb5986</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer - TS/SCI with Polygraph</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
+          <t>https://www.indeed.com/viewjob?jk=b0792aed4e33e1fc</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Java Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e0df5a13808e32</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Healthix</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Spark Streaming, Kafka, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51729f31816ec17</t>
+          <t>https://www.indeed.com/viewjob?jk=1bf44e9b8dd895de</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Radiant Digital</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72e4768c31a35e7d</t>
+          <t>https://www.indeed.com/viewjob?jk=d716d1e9dd6e4b0b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer III: Machine Learning Platform</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4efec6d9008a5b85</t>
+          <t>https://www.indeed.com/viewjob?jk=34e86f2f2a315595</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Backend - AI Search</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,49 +1406,49 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16388829699da902</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8d99a7003ab349</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
+          <t>https://www.indeed.com/viewjob?jk=ee3c21dbe995c8b9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Java Consultant</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1462,326 +1462,326 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Backend Developer - .NET &amp; Azure</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Reidy</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
+          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=239b1046f06d3d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=6a56c54d2027c92d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a7f6dab575a97ad</t>
+          <t>https://www.indeed.com/viewjob?jk=11dd4db7d11a9ebd</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02a598ce56d257c</t>
+          <t>https://www.indeed.com/viewjob?jk=29610b7eba9cc4cb</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b64bf3747c350d3</t>
+          <t>https://www.indeed.com/viewjob?jk=693bc93cfe95e968</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FundMate LLC</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d833bbf779bc5e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=fafa6085d07ec220</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab66e7fa68e90c6</t>
+          <t>https://www.indeed.com/viewjob?jk=71120e321dbd18c4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
+          <t>https://www.indeed.com/viewjob?jk=be687a9701ed10cb</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Systems Administrator</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>HH Brown Shoe Company</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Martinsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
+          <t>https://www.indeed.com/viewjob?jk=0bca63db22516c1c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
+          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Software Engineer - TS/SCI with Polygraph</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=929003fb57aecac9</t>
+          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,49 +1931,49 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Operations Analytics Data Scientist</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RadNet</t>
+          <t>Healthix</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=b51729f31816ec17</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Vector Database Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1987,11 +1987,11 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,19 +2001,19 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
+          <t>https://www.indeed.com/viewjob?jk=954fc9353b3c1ac7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DBHDS - SQL Database Administrator</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Betis Group, Inc.</t>
+          <t>Radiant Digital</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2031,142 +2031,142 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
+          <t>https://www.indeed.com/viewjob?jk=72e4768c31a35e7d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Kimco Realty Corporation</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=4efec6d9008a5b85</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Application Developer Sr II</t>
+          <t>Java Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
+          <t>https://www.indeed.com/viewjob?jk=e34601ff78d0fbb8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Application Developer Sr I</t>
+          <t>Spring/Spring Boot Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
+          <t>https://www.indeed.com/viewjob?jk=fe5d1444b8c11690</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Java Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
+          <t>https://www.indeed.com/viewjob?jk=8ff0ce794c90e055</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Senior Software Engineer II - Backend - AI Search</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=16388829699da902</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SiriusXM</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
+          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Java Consultant</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>adswizz</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
+          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Backend Developer - .NET &amp; Azure</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Reidy</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,102 +2316,102 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
+          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
+          <t>https://www.indeed.com/viewjob?jk=239b1046f06d3d2f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
+          <t>https://www.indeed.com/viewjob?jk=3a7f6dab575a97ad</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
+          <t>https://www.indeed.com/viewjob?jk=d02a598ce56d257c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
+          <t>https://www.indeed.com/viewjob?jk=0b64bf3747c350d3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>FundMate LLC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
+          <t>https://www.indeed.com/viewjob?jk=d833bbf779bc5e9f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BI Engineer , BI Center of Excellence</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Evolent</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,67 +2561,67 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab66e7fa68e90c6</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
+          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,77 +2666,1197 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer (Hybrid)</t>
+          <t>Spring/Spring Boot Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Westerra Credit Union</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff473c63d82167e1</t>
+          <t>https://www.indeed.com/viewjob?jk=e62470d61b3dfe4f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Knightscope, Inc.</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=929003fb57aecac9</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Evercommerce</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Operations Analytics Data Scientist</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>RadNet</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>MD, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Vector Database Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ed3da09014d75be</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Kafka Real Time Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Vector Database Engineer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>DBHDS - SQL Database Administrator</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Betis Group, Inc.</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Kimco Realty Corporation</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Jericho, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Application Developer Sr II</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>IDEXX Laboratories</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Portland, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Application Developer Sr I</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>IDEXX Laboratories</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Portland, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Minnetonka, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Data Analytics &amp; BI with Tableau</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Data Engineer III</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>SiriusXM</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Data Engineer III</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>adswizz</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer New</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Chantilly, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer-AI</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Thomson Reuters</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Frisco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SS&amp;C</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>AWS Network Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>TeraWatt Infrastructure</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>VeeRteq Solutions Inc.</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>AWS Network Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>AMH</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Draper, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>BI Engineer , BI Center of Excellence</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Evolent</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Scala Architect</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dcabbff9d7acb5a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>HealthEdge Software, Inc.</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Bank of America</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
           <t>Commercial Operations BI Analyst</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>Colgate-Palmolive</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
-      <c r="D66" t="n">
+      <c r="D94" t="n">
         <v>10.4</v>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Business Intelligence Developer (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Westerra Credit Union</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff473c63d82167e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>ML Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a246f2fce8506457</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>ML Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=838425ec33e5fff1</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>ML Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbf17f38d746779a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-17.xlsx
+++ b/results/job_matches_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,130 +468,130 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer (Remote)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19.4</v>
+        <v>25.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Flume, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36bcd88655ec26b</t>
+          <t>https://www.indeed.com/viewjob?jk=31ac562fdbccfcbb</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, SQL Server</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=342faa6b5c9756a2</t>
+          <t>https://www.indeed.com/viewjob?jk=b36bcd88655ec26b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be2803455ebf096</t>
+          <t>https://www.indeed.com/viewjob?jk=342faa6b5c9756a2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tapouts</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Venice, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcb6f48928a08bed</t>
+          <t>https://www.indeed.com/viewjob?jk=5be2803455ebf096</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Glue</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tapouts</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Venice, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,19 +636,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c8436cd0c6787a</t>
+          <t>https://www.indeed.com/viewjob?jk=bcb6f48928a08bed</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Agile Developer - Datamart</t>
+          <t>Software Engineer III - AWS Glue</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b0a1eacc51b9571</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c8436cd0c6787a</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15708f0e06d200c6</t>
+          <t>https://www.indeed.com/viewjob?jk=8b0a1eacc51b9571</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Sr Agile Developer - Datamart</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b271d311d5d546b6</t>
+          <t>https://www.indeed.com/viewjob?jk=15708f0e06d200c6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ARCHKEY SOLUTIONS</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fenton, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,42 +776,42 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecdbaaed7feccfa0</t>
+          <t>https://www.indeed.com/viewjob?jk=b271d311d5d546b6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ARCHKEY SOLUTIONS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fenton, MO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd7396ffb6ba90c</t>
+          <t>https://www.indeed.com/viewjob?jk=ecdbaaed7feccfa0</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Azure ETL Developer with Advance Power BI Experience - Public transportation domain experience</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Syncreon Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c016dae6a0a4e49</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd7396ffb6ba90c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cloud-Native MLOps Engineer</t>
+          <t>Azure ETL Developer with Advance Power BI Experience - Public transportation domain experience</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Syncreon Consulting</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a456d96d929a416c</t>
+          <t>https://www.indeed.com/viewjob?jk=4c016dae6a0a4e49</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kafka API Gateway Engineer</t>
+          <t>Cloud-Native MLOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5ee5a6cd78dc32</t>
+          <t>https://www.indeed.com/viewjob?jk=a456d96d929a416c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Kafka API Gateway Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fb3549614f234b2</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5ee5a6cd78dc32</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CPI Security</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e81977d38af04d</t>
+          <t>https://www.indeed.com/viewjob?jk=8fb3549614f234b2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kafka Spark Streaming Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Lambda, S3, IAM, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cb2fd809795c0f</t>
+          <t>https://www.indeed.com/viewjob?jk=c8e81977d38af04d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ETL Data Engineer</t>
+          <t>Kafka Spark Streaming Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hays</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Carolina, PR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, Kafka, Oracle</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=233a1a341ad0aa38</t>
+          <t>https://www.indeed.com/viewjob?jk=96cb2fd809795c0f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>ETL Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>Hays</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Carolina, PR, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, ECS, RDS, Azure, Databricks, Cloud Storage</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e7128e441d147a</t>
+          <t>https://www.indeed.com/viewjob?jk=233a1a341ad0aa38</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, ECS, RDS, Azure, Databricks, Cloud Storage</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5861e377dbf3fbc8</t>
+          <t>https://www.indeed.com/viewjob?jk=33e7128e441d147a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Flask Architect</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e317c65dceb5986</t>
+          <t>https://www.indeed.com/viewjob?jk=5861e377dbf3fbc8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Flask Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0792aed4e33e1fc</t>
+          <t>https://www.indeed.com/viewjob?jk=7e317c65dceb5986</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Java Architect</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1e0df5a13808e32</t>
+          <t>https://www.indeed.com/viewjob?jk=b0792aed4e33e1fc</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Java Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1287,11 +1287,11 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Spark Streaming, Kafka, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,14 +1301,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bf44e9b8dd895de</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e0df5a13808e32</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Spark Streaming, Kafka, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d716d1e9dd6e4b0b</t>
+          <t>https://www.indeed.com/viewjob?jk=1bf44e9b8dd895de</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer III: Machine Learning Platform</t>
+          <t>Data Engineer (No Sponsorship Available)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Heritage Construction + Materials</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34e86f2f2a315595</t>
+          <t>https://www.indeed.com/viewjob?jk=8313f5120d5c6237</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8d99a7003ab349</t>
+          <t>https://www.indeed.com/viewjob?jk=d716d1e9dd6e4b0b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III: Machine Learning Platform</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,59 +1441,59 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee3c21dbe995c8b9</t>
+          <t>https://www.indeed.com/viewjob?jk=34e86f2f2a315595</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8d99a7003ab349</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
+          <t>https://www.indeed.com/viewjob?jk=ee3c21dbe995c8b9</t>
         </is>
       </c>
     </row>
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
+          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a56c54d2027c92d</t>
+          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11dd4db7d11a9ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29610b7eba9cc4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=6a56c54d2027c92d</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693bc93cfe95e968</t>
+          <t>https://www.indeed.com/viewjob?jk=11dd4db7d11a9ebd</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fafa6085d07ec220</t>
+          <t>https://www.indeed.com/viewjob?jk=29610b7eba9cc4cb</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71120e321dbd18c4</t>
+          <t>https://www.indeed.com/viewjob?jk=693bc93cfe95e968</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be687a9701ed10cb</t>
+          <t>https://www.indeed.com/viewjob?jk=fafa6085d07ec220</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Systems Administrator</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HH Brown Shoe Company</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Martinsburg, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bca63db22516c1c</t>
+          <t>https://www.indeed.com/viewjob?jk=71120e321dbd18c4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
+          <t>https://www.indeed.com/viewjob?jk=be687a9701ed10cb</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer - TS/SCI with Polygraph</t>
+          <t>Systems Administrator</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>HH Brown Shoe Company</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Martinsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
+          <t>https://www.indeed.com/viewjob?jk=0bca63db22516c1c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,77 +1921,77 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
+          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Software Engineer - TS/SCI with Polygraph</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Healthix</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
+          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51729f31816ec17</t>
+          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=954fc9353b3c1ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Radiant Digital</t>
+          <t>Healthix</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72e4768c31a35e7d</t>
+          <t>https://www.indeed.com/viewjob?jk=b51729f31816ec17</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2078,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Java Architect</t>
+          <t>Data Architect (Databricks)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>VTekis Consulting LLP</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,14 +2106,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34601ff78d0fbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=8e81f0056e0c1281</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Spring/Spring Boot Architect</t>
+          <t>Java Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2141,14 +2141,14 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe5d1444b8c11690</t>
+          <t>https://www.indeed.com/viewjob?jk=e34601ff78d0fbb8</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Java Architect</t>
+          <t>Spring/Spring Boot Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ff0ce794c90e055</t>
+          <t>https://www.indeed.com/viewjob?jk=fe5d1444b8c11690</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Backend - AI Search</t>
+          <t>Java Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16388829699da902</t>
+          <t>https://www.indeed.com/viewjob?jk=8ff0ce794c90e055</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
+          <t>https://www.indeed.com/viewjob?jk=03ea3f0ee7726aea</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Java Consultant</t>
+          <t>Senior Software Engineer II - Backend - AI Search</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=16388829699da902</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Backend Developer - .NET &amp; Azure</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Reidy</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
+          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Java Consultant</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Backend Developer - .NET &amp; Azure</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Reidy</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=239b1046f06d3d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a7f6dab575a97ad</t>
+          <t>https://www.indeed.com/viewjob?jk=239b1046f06d3d2f</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02a598ce56d257c</t>
+          <t>https://www.indeed.com/viewjob?jk=3a7f6dab575a97ad</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b64bf3747c350d3</t>
+          <t>https://www.indeed.com/viewjob?jk=d02a598ce56d257c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FundMate LLC</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d833bbf779bc5e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=0b64bf3747c350d3</t>
         </is>
       </c>
     </row>
@@ -2603,17 +2603,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Spring/Spring Boot Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,139 +2621,139 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
+          <t>https://www.indeed.com/viewjob?jk=e62470d61b3dfe4f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
+          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Spring/Spring Boot Architect</t>
+          <t>Operations Analytics Data Scientist</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RadNet</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e62470d61b3dfe4f</t>
+          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Full Stack Engineer, Senior</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=929003fb57aecac9</t>
+          <t>https://www.indeed.com/viewjob?jk=c00e725f72169245</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
+          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Operations Analytics Data Scientist</t>
+          <t>Vector Database Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>RadNet</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Vector Database Engineer</t>
+          <t>DBHDS - SQL Database Administrator</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Betis Group, Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2836,29 +2836,29 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ed3da09014d75be</t>
+          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kimco Realty Corporation</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
+          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Vector Database Engineer</t>
+          <t>Application Developer Sr II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
+          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DBHDS - SQL Database Administrator</t>
+          <t>Application Developer Sr I</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Betis Group, Inc.</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
+          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Kimco Realty Corporation</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Application Developer Sr II</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
+          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Application Developer Sr I</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>SiriusXM</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,49 +3051,49 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
+          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>adswizz</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
+          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3103,15 +3103,15 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Machine Learning Engineer New</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SiriusXM</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
+          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Platform Engineer-AI</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>adswizz</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
+          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer New</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-AI</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>TeraWatt Infrastructure</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,17 +3321,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
+          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
         </is>
       </c>
     </row>
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
+          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
+          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>BI Engineer , BI Center of Excellence</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Evolent</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
+          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Scala Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+          <t>Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
+          <t>https://www.indeed.com/viewjob?jk=dcabbff9d7acb5a5</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BI Engineer , BI Center of Excellence</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Evolent</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
+          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Scala Architect</t>
+          <t>Commercial Operations BI Analyst</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcabbff9d7acb5a5</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Business Intelligence Developer (Hybrid)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>Westerra Credit Union</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
+          <t>https://www.indeed.com/viewjob?jk=ff473c63d82167e1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>ML Platform Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=a246f2fce8506457</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
+          <t>ML Platform Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
+          <t>https://www.indeed.com/viewjob?jk=838425ec33e5fff1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Commercial Operations BI Analyst</t>
+          <t>ML Platform Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,155 +3706,15 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Westerra Credit Union</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff473c63d82167e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>ML Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a246f2fce8506457</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>ML Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=838425ec33e5fff1</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>ML Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fbf17f38d746779a</t>
         </is>

--- a/results/job_matches_2026-03-17.xlsx
+++ b/results/job_matches_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Flask Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5861e377dbf3fbc8</t>
+          <t>https://www.indeed.com/viewjob?jk=7e317c65dceb5986</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Flask Architect</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e317c65dceb5986</t>
+          <t>https://www.indeed.com/viewjob?jk=b0792aed4e33e1fc</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Java Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0792aed4e33e1fc</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e0df5a13808e32</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Java Architect</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1287,11 +1287,11 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Spark, Scala, Kafka</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Spark Streaming, Kafka, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1e0df5a13808e32</t>
+          <t>https://www.indeed.com/viewjob?jk=1bf44e9b8dd895de</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Data Engineer (No Sponsorship Available)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Heritage Construction + Materials</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Spark Streaming, Kafka, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bf44e9b8dd895de</t>
+          <t>https://www.indeed.com/viewjob?jk=8313f5120d5c6237</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer (No Sponsorship Available)</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Heritage Construction + Materials</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8313f5120d5c6237</t>
+          <t>https://www.indeed.com/viewjob?jk=d716d1e9dd6e4b0b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Software Engineer III: Machine Learning Platform</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d716d1e9dd6e4b0b</t>
+          <t>https://www.indeed.com/viewjob?jk=34e86f2f2a315595</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer III: Machine Learning Platform</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,69 +1431,69 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34e86f2f2a315595</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8d99a7003ab349</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8d99a7003ab349</t>
+          <t>https://www.indeed.com/viewjob?jk=ee3c21dbe995c8b9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee3c21dbe995c8b9</t>
+          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
+          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
         </is>
       </c>
     </row>
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
+          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
+          <t>https://www.indeed.com/viewjob?jk=6a56c54d2027c92d</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a56c54d2027c92d</t>
+          <t>https://www.indeed.com/viewjob?jk=11dd4db7d11a9ebd</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11dd4db7d11a9ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=29610b7eba9cc4cb</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29610b7eba9cc4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=693bc93cfe95e968</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693bc93cfe95e968</t>
+          <t>https://www.indeed.com/viewjob?jk=fafa6085d07ec220</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fafa6085d07ec220</t>
+          <t>https://www.indeed.com/viewjob?jk=71120e321dbd18c4</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71120e321dbd18c4</t>
+          <t>https://www.indeed.com/viewjob?jk=be687a9701ed10cb</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Systems Administrator</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>HH Brown Shoe Company</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Martinsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be687a9701ed10cb</t>
+          <t>https://www.indeed.com/viewjob?jk=0bca63db22516c1c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Systems Administrator</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HH Brown Shoe Company</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Martinsburg, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bca63db22516c1c</t>
+          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,77 +1921,77 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer - TS/SCI with Polygraph</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Healthix</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
+          <t>https://www.indeed.com/viewjob?jk=b51729f31816ec17</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
+          <t>https://www.indeed.com/viewjob?jk=4efec6d9008a5b85</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Healthix</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51729f31816ec17</t>
+          <t>https://www.indeed.com/viewjob?jk=03ea3f0ee7726aea</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Architect (Databricks)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>VTekis Consulting LLP</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4efec6d9008a5b85</t>
+          <t>https://www.indeed.com/viewjob?jk=8e81f0056e0c1281</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Architect (Databricks)</t>
+          <t>Java Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>VTekis Consulting LLP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Databricks Lakehouse</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,14 +2106,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e81f0056e0c1281</t>
+          <t>https://www.indeed.com/viewjob?jk=e34601ff78d0fbb8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Java Architect</t>
+          <t>Spring/Spring Boot Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2141,14 +2141,14 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34601ff78d0fbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=fe5d1444b8c11690</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Spring/Spring Boot Architect</t>
+          <t>Java Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe5d1444b8c11690</t>
+          <t>https://www.indeed.com/viewjob?jk=8ff0ce794c90e055</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Java Architect</t>
+          <t>Senior Software Engineer II - Backend - AI Search</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ff0ce794c90e055</t>
+          <t>https://www.indeed.com/viewjob?jk=16388829699da902</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ea3f0ee7726aea</t>
+          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Backend - AI Search</t>
+          <t>Java Consultant</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16388829699da902</t>
+          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Backend Developer - .NET &amp; Azure</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Reidy</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
+          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Java Consultant</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=239b1046f06d3d2f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Backend Developer - .NET &amp; Azure</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Reidy</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
+          <t>https://www.indeed.com/viewjob?jk=3a7f6dab575a97ad</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=239b1046f06d3d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=d02a598ce56d257c</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a7f6dab575a97ad</t>
+          <t>https://www.indeed.com/viewjob?jk=0b64bf3747c350d3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, S3, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,59 +2491,59 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02a598ce56d257c</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab66e7fa68e90c6</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b64bf3747c350d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab66e7fa68e90c6</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
         </is>
       </c>
     </row>
@@ -2603,17 +2603,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Spring/Spring Boot Architect</t>
+          <t>Mgr Software Development- REMOTE</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AnswerNet</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e62470d61b3dfe4f</t>
+          <t>https://www.indeed.com/viewjob?jk=3a865f04fb8b0cdc</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
+          <t>Spring/Spring Boot Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
+          <t>https://www.indeed.com/viewjob?jk=e62470d61b3dfe4f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Operations Analytics Data Scientist</t>
+          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RadNet</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
+          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior</t>
+          <t>Operations Analytics Data Scientist</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>RadNet</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00e725f72169245</t>
+          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Goodwill Industries of Ky., Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
+          <t>https://www.indeed.com/viewjob?jk=6c96bce5537ab08e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Vector Database Engineer</t>
+          <t>Full Stack Engineer, Senior</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
+          <t>https://www.indeed.com/viewjob?jk=c00e725f72169245</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DBHDS - SQL Database Administrator</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Betis Group, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
+          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Vector Database Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Kimco Realty Corporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Application Developer Sr II</t>
+          <t>DBHDS - SQL Database Administrator</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Betis Group, Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
+          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Application Developer Sr I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Kimco Realty Corporation</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
+          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Application Developer Sr II</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
+          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Application Developer Sr I</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,19 +3016,19 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SiriusXM</t>
+          <t>Open Lending</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3037,143 +3037,143 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Polars, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
+          <t>https://www.indeed.com/viewjob?jk=980979d9074d5784</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>adswizz</t>
+          <t>Open Lending</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Polars, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
+          <t>https://www.indeed.com/viewjob?jk=46dca6f38ea157d1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer New</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
+          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-AI</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>SiriusXM</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
+          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>adswizz</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
+          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
+          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
+          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer New</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
+          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Platform Engineer-AI</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
+          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
+          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BI Engineer , BI Center of Excellence</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Evolent</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Scala Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TeraWatt Infrastructure</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcabbff9d7acb5a5</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
+          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Commercial Operations BI Analyst</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
+          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer (Hybrid)</t>
+          <t>Scala Architect</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Westerra Credit Union</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
+          <t>Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff473c63d82167e1</t>
+          <t>https://www.indeed.com/viewjob?jk=dcabbff9d7acb5a5</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ML Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a246f2fce8506457</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ML Platform Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=838425ec33e5fff1</t>
+          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ML Platform Engineer</t>
+          <t>Business Intelligence Developer (Hybrid)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Westerra Credit Union</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,15 +3706,155 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
+          <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff473c63d82167e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Commercial Operations BI Analyst</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Colgate-Palmolive</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Piscataway, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>ML Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
           <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a246f2fce8506457</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>ML Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=838425ec33e5fff1</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>ML Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fbf17f38d746779a</t>
         </is>

--- a/results/job_matches_2026-03-17.xlsx
+++ b/results/job_matches_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Java Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ea3f0ee7726aea</t>
+          <t>https://www.indeed.com/viewjob?jk=e34601ff78d0fbb8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Architect (Databricks)</t>
+          <t>Spring/Spring Boot Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>VTekis Consulting LLP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Databricks Lakehouse</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e81f0056e0c1281</t>
+          <t>https://www.indeed.com/viewjob?jk=fe5d1444b8c11690</t>
         </is>
       </c>
     </row>
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34601ff78d0fbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=8ff0ce794c90e055</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Spring/Spring Boot Architect</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe5d1444b8c11690</t>
+          <t>https://www.indeed.com/viewjob?jk=03ea3f0ee7726aea</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Java Architect</t>
+          <t>Senior Software Engineer II - Backend - AI Search</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ff0ce794c90e055</t>
+          <t>https://www.indeed.com/viewjob?jk=16388829699da902</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Backend - AI Search</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16388829699da902</t>
+          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Java Consultant</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
+          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Java Consultant</t>
+          <t>Backend Developer - .NET &amp; Azure</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Reidy</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Backend Developer - .NET &amp; Azure</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Reidy</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,164 +2316,164 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab66e7fa68e90c6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Junior Software Development Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=239b1046f06d3d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a7f6dab575a97ad</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02a598ce56d257c</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b64bf3747c350d3</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Spring/Spring Boot Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,42 +2481,42 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab66e7fa68e90c6</t>
+          <t>https://www.indeed.com/viewjob?jk=e62470d61b3dfe4f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics</t>
+          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
+          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,67 +2526,67 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
+          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics</t>
+          <t>Operations Analytics Data Scientist</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>RadNet</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Goodwill Industries of Ky., Inc.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
+          <t>https://www.indeed.com/viewjob?jk=6c96bce5537ab08e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mgr Software Development- REMOTE</t>
+          <t>Full Stack Engineer, Senior</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AnswerNet</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a865f04fb8b0cdc</t>
+          <t>https://www.indeed.com/viewjob?jk=c00e725f72169245</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Spring/Spring Boot Architect</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2652,11 +2652,11 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e62470d61b3dfe4f</t>
+          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
+          <t>Vector Database Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
+          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Operations Analytics Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RadNet</t>
+          <t>Kimco Realty Corporation</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Application Developer Sr II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Goodwill Industries of Ky., Inc.</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c96bce5537ab08e</t>
+          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior</t>
+          <t>Application Developer Sr I</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00e725f72169245</t>
+          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Open Lending</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Polars, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
+          <t>https://www.indeed.com/viewjob?jk=980979d9074d5784</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Vector Database Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Open Lending</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Polars, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
+          <t>https://www.indeed.com/viewjob?jk=46dca6f38ea157d1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DBHDS - SQL Database Administrator</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Betis Group, Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Kimco Realty Corporation</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Application Developer Sr II</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>SiriusXM</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
+          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Application Developer Sr I</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>adswizz</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,67 +3016,67 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
+          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Open Lending</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Polars, Power BI, Tableau, MLOps</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=980979d9074d5784</t>
+          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Open Lending</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Polars, Power BI, Tableau, MLOps</t>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46dca6f38ea157d1</t>
+          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Machine Learning Engineer New</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,59 +3121,59 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
+          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Senior Platform Engineer-AI</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SiriusXM</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
+          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>adswizz</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>TeraWatt Infrastructure</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
+          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer New</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
+          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-AI</t>
+          <t>Scala Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
+          <t>https://www.indeed.com/viewjob?jk=dcabbff9d7acb5a5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Business Intelligence Developer (Hybrid)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Westerra Credit Union</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
+          <t>https://www.indeed.com/viewjob?jk=ff473c63d82167e1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Commercial Operations BI Analyst</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ML Platform Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,24 +3496,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
+          <t>https://www.indeed.com/viewjob?jk=a246f2fce8506457</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>ML Platform Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
+          <t>https://www.indeed.com/viewjob?jk=838425ec33e5fff1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>ML Platform Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,295 +3566,15 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Scala Architect</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dcabbff9d7acb5a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>HealthEdge Software, Inc.</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Westerra Credit Union</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff473c63d82167e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Commercial Operations BI Analyst</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Colgate-Palmolive</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Piscataway, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>ML Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a246f2fce8506457</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>ML Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=838425ec33e5fff1</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>ML Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fbf17f38d746779a</t>
         </is>

--- a/results/job_matches_2026-03-17.xlsx
+++ b/results/job_matches_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,95 +503,95 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer (Remote)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Flume, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36bcd88655ec26b</t>
+          <t>https://www.indeed.com/viewjob?jk=342faa6b5c9756a2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=342faa6b5c9756a2</t>
+          <t>https://www.indeed.com/viewjob?jk=5be2803455ebf096</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tapouts</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Venice, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be2803455ebf096</t>
+          <t>https://www.indeed.com/viewjob?jk=bcb6f48928a08bed</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - AWS Glue</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tapouts</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Venice, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,19 +636,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcb6f48928a08bed</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c8436cd0c6787a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Glue</t>
+          <t>Sr Agile Developer - Datamart</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c8436cd0c6787a</t>
+          <t>https://www.indeed.com/viewjob?jk=8b0a1eacc51b9571</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b0a1eacc51b9571</t>
+          <t>https://www.indeed.com/viewjob?jk=15708f0e06d200c6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Agile Developer - Datamart</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15708f0e06d200c6</t>
+          <t>https://www.indeed.com/viewjob?jk=b271d311d5d546b6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ARCHKEY SOLUTIONS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fenton, MO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,42 +776,42 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b271d311d5d546b6</t>
+          <t>https://www.indeed.com/viewjob?jk=ecdbaaed7feccfa0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ARCHKEY SOLUTIONS</t>
+          <t>Creative Global Consulting</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fenton, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecdbaaed7feccfa0</t>
+          <t>https://www.indeed.com/viewjob?jk=839384e124811ed2</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Snowflake Architect Needed --- Local to Bay Area California</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deltasoft Solutions LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Spark Streaming, Kafka, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bf44e9b8dd895de</t>
+          <t>https://www.indeed.com/viewjob?jk=db48c42eace691bd</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer (No Sponsorship Available)</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Heritage Construction + Materials</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Spark Streaming, Kafka, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8313f5120d5c6237</t>
+          <t>https://www.indeed.com/viewjob?jk=1bf44e9b8dd895de</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Data Engineer (No Sponsorship Available)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Heritage Construction + Materials</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d716d1e9dd6e4b0b</t>
+          <t>https://www.indeed.com/viewjob?jk=8313f5120d5c6237</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer III: Machine Learning Platform</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34e86f2f2a315595</t>
+          <t>https://www.indeed.com/viewjob?jk=d716d1e9dd6e4b0b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Software Engineer III: Machine Learning Platform</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8d99a7003ab349</t>
+          <t>https://www.indeed.com/viewjob?jk=34e86f2f2a315595</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7364dc6344381a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
+          <t>https://www.indeed.com/viewjob?jk=40e5ace322ab3dae</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
+          <t>https://www.indeed.com/viewjob?jk=101461b42f2929c7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a56c54d2027c92d</t>
+          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11dd4db7d11a9ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29610b7eba9cc4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693bc93cfe95e968</t>
+          <t>https://www.indeed.com/viewjob?jk=6a56c54d2027c92d</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fafa6085d07ec220</t>
+          <t>https://www.indeed.com/viewjob?jk=11dd4db7d11a9ebd</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71120e321dbd18c4</t>
+          <t>https://www.indeed.com/viewjob?jk=29610b7eba9cc4cb</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be687a9701ed10cb</t>
+          <t>https://www.indeed.com/viewjob?jk=693bc93cfe95e968</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Systems Administrator</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HH Brown Shoe Company</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Martinsburg, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bca63db22516c1c</t>
+          <t>https://www.indeed.com/viewjob?jk=fafa6085d07ec220</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
+          <t>https://www.indeed.com/viewjob?jk=71120e321dbd18c4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
+          <t>https://www.indeed.com/viewjob?jk=be687a9701ed10cb</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Systems Administrator</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Healthix</t>
+          <t>HH Brown Shoe Company</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Martinsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51729f31816ec17</t>
+          <t>https://www.indeed.com/viewjob?jk=0bca63db22516c1c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4efec6d9008a5b85</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Java Architect</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Healthix</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34601ff78d0fbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=b51729f31816ec17</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Spring/Spring Boot Architect</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe5d1444b8c11690</t>
+          <t>https://www.indeed.com/viewjob?jk=4efec6d9008a5b85</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Java Architect</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ff0ce794c90e055</t>
+          <t>https://www.indeed.com/viewjob?jk=03ea3f0ee7726aea</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Java Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ea3f0ee7726aea</t>
+          <t>https://www.indeed.com/viewjob?jk=e34601ff78d0fbb8</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Backend - AI Search</t>
+          <t>Spring/Spring Boot Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16388829699da902</t>
+          <t>https://www.indeed.com/viewjob?jk=fe5d1444b8c11690</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Java Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
+          <t>https://www.indeed.com/viewjob?jk=8ff0ce794c90e055</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Java Consultant</t>
+          <t>Senior Software Engineer II - Backend - AI Search</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=16388829699da902</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Backend Developer - .NET &amp; Azure</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Reidy</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
+          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Java Consultant</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab66e7fa68e90c6</t>
+          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Junior Software Development Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab66e7fa68e90c6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
+          <t>https://www.indeed.com/viewjob?jk=50effdd5410c6590</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics</t>
+          <t>Senior Data Engineer (Snowflake/dbt/Healthcare) - 100% Remote</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Blue Sky Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=2e0e6e4a15258683</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Junior Software Development Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
+          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Spring/Spring Boot Architect</t>
+          <t>Senior Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e62470d61b3dfe4f</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
+          <t>Senior Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,67 +2526,67 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Operations Analytics Data Scientist</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RadNet</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Spring/Spring Boot Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Goodwill Industries of Ky., Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c96bce5537ab08e</t>
+          <t>https://www.indeed.com/viewjob?jk=e62470d61b3dfe4f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior</t>
+          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00e725f72169245</t>
+          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Operations Analytics Data Scientist</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RadNet</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
+          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Vector Database Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Northwestern Mutual</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Snowflake, ELT, dbt, Power BI, Tableau, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
+          <t>https://www.indeed.com/viewjob?jk=12eceb4f7778f690</t>
         </is>
       </c>
     </row>
@@ -2713,12 +2713,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Kimco Realty Corporation</t>
+          <t>Goodwill Industries of Ky., Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=6c96bce5537ab08e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Application Developer Sr II</t>
+          <t>Full Stack Engineer, Senior</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
+          <t>https://www.indeed.com/viewjob?jk=c00e725f72169245</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Application Developer Sr I</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
+          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Vector Database Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Open Lending</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Polars, Power BI, Tableau, MLOps</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=980979d9074d5784</t>
+          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Open Lending</t>
+          <t>Kimco Realty Corporation</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Polars, Power BI, Tableau, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46dca6f38ea157d1</t>
+          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Application Developer Sr II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
+          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Application Developer Sr I</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,19 +2946,19 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SiriusXM</t>
+          <t>Open Lending</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2967,63 +2967,63 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Polars, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
+          <t>https://www.indeed.com/viewjob?jk=980979d9074d5784</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>adswizz</t>
+          <t>Open Lending</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Polars, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
+          <t>https://www.indeed.com/viewjob?jk=46dca6f38ea157d1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3033,50 +3033,50 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
+          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer New</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,59 +3121,59 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-AI</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
+          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>SiriusXM</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
+          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>adswizz</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
+          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
+          <t>https://www.indeed.com/viewjob?jk=b27aedc78511ea81</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
+          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Machine Learning Engineer New</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
+          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Scala Architect</t>
+          <t>Senior Platform Engineer-AI</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcabbff9d7acb5a5</t>
+          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
+          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer (Hybrid)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Westerra Credit Union</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff473c63d82167e1</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Commercial Operations BI Analyst</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>TeraWatt Infrastructure</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ML Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,24 +3496,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a246f2fce8506457</t>
+          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ML Platform Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3531,24 +3531,24 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=838425ec33e5fff1</t>
+          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ML Platform Engineer</t>
+          <t>Scala Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3566,17 +3566,227 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
+          <t>Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dcabbff9d7acb5a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>HealthEdge Software, Inc.</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Business Intelligence Developer (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Westerra Credit Union</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff473c63d82167e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ML Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
           <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a246f2fce8506457</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>ML Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=838425ec33e5fff1</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>ML Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fbf17f38d746779a</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Avaya</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93cc248964e1485d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-17.xlsx
+++ b/results/job_matches_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior Software Engineer (ServiceNow)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Hotwire Communications</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be2803455ebf096</t>
+          <t>https://www.indeed.com/viewjob?jk=8a28cfe9183e3c37</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tapouts</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Venice, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcb6f48928a08bed</t>
+          <t>https://www.indeed.com/viewjob?jk=5be2803455ebf096</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Glue</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tapouts</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Venice, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,19 +636,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c8436cd0c6787a</t>
+          <t>https://www.indeed.com/viewjob?jk=bcb6f48928a08bed</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Agile Developer - Datamart</t>
+          <t>Software Engineer III - AWS Glue</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b0a1eacc51b9571</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c8436cd0c6787a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Agile Developer - Datamart</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Arrow International</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15708f0e06d200c6</t>
+          <t>https://www.indeed.com/viewjob?jk=25c3c576bdca9fea</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Sr Agile Developer - Datamart</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b271d311d5d546b6</t>
+          <t>https://www.indeed.com/viewjob?jk=8b0a1eacc51b9571</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Sr Agile Developer - Datamart</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ARCHKEY SOLUTIONS</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fenton, MO, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,104 +766,104 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecdbaaed7feccfa0</t>
+          <t>https://www.indeed.com/viewjob?jk=15708f0e06d200c6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Creative Global Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Cloud Storage, Spark, PySpark</t>
+          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=839384e124811ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=b271d311d5d546b6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior DevOps Cloud Engineer</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ARCHKEY SOLUTIONS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Fenton, MO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f9a6991656b7b52</t>
+          <t>https://www.indeed.com/viewjob?jk=ecdbaaed7feccfa0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Creative Global Consulting</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd7396ffb6ba90c</t>
+          <t>https://www.indeed.com/viewjob?jk=839384e124811ed2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Azure ETL Developer with Advance Power BI Experience - Public transportation domain experience</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Syncreon Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c016dae6a0a4e49</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd7396ffb6ba90c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cloud-Native MLOps Engineer</t>
+          <t>Azure ETL Developer with Advance Power BI Experience - Public transportation domain experience</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Syncreon Consulting</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a456d96d929a416c</t>
+          <t>https://www.indeed.com/viewjob?jk=4c016dae6a0a4e49</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kafka API Gateway Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ConcertAI</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plymouth Meeting, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Redshift, Step Functions, RDS, Databricks, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5ee5a6cd78dc32</t>
+          <t>https://www.indeed.com/viewjob?jk=46a6962bac387525</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kafka Support Analyst</t>
+          <t>Cloud-Native MLOps Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fb3549614f234b2</t>
+          <t>https://www.indeed.com/viewjob?jk=a456d96d929a416c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kafka API Gateway Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CPI Security</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,24 +1046,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e81977d38af04d</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5ee5a6cd78dc32</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kafka Spark Streaming Engineer</t>
+          <t>Kafka Support Analyst</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Spark, Scala, Spark Streaming</t>
+          <t>AWS, EMR, Redshift, Azure, Databricks, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cb2fd809795c0f</t>
+          <t>https://www.indeed.com/viewjob?jk=8fb3549614f234b2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ETL Data Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hays</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Carolina, PR, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,42 +1116,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, Kafka, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=233a1a341ad0aa38</t>
+          <t>https://www.indeed.com/viewjob?jk=025286b55c821347</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, ECS, RDS, Azure, Databricks, Cloud Storage</t>
+          <t>AWS, Lambda, S3, IAM, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e7128e441d147a</t>
+          <t>https://www.indeed.com/viewjob?jk=c8e81977d38af04d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Flask Architect</t>
+          <t>Kafka Spark Streaming Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,49 +1196,49 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e317c65dceb5986</t>
+          <t>https://www.indeed.com/viewjob?jk=96cb2fd809795c0f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>ETL Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Hays</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Carolina, PR, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0792aed4e33e1fc</t>
+          <t>https://www.indeed.com/viewjob?jk=233a1a341ad0aa38</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Java Architect</t>
+          <t>Flask Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1e0df5a13808e32</t>
+          <t>https://www.indeed.com/viewjob?jk=7e317c65dceb5986</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Snowflake Architect Needed --- Local to Bay Area California</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Deltasoft Solutions LLC</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,14 +1301,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db48c42eace691bd</t>
+          <t>https://www.indeed.com/viewjob?jk=b0792aed4e33e1fc</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Java Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1322,11 +1322,11 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Spark Streaming, Kafka, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bf44e9b8dd895de</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e0df5a13808e32</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer (No Sponsorship Available)</t>
+          <t>Snowflake Architect Needed --- Local to Bay Area California</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Heritage Construction + Materials</t>
+          <t>Deltasoft Solutions LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8313f5120d5c6237</t>
+          <t>https://www.indeed.com/viewjob?jk=db48c42eace691bd</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Spark Streaming, Kafka, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d716d1e9dd6e4b0b</t>
+          <t>https://www.indeed.com/viewjob?jk=1bf44e9b8dd895de</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer III: Machine Learning Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34e86f2f2a315595</t>
+          <t>https://www.indeed.com/viewjob?jk=d916292cc6da2afe</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (No Sponsorship Available)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Heritage Construction + Materials</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee3c21dbe995c8b9</t>
+          <t>https://www.indeed.com/viewjob?jk=8313f5120d5c6237</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7364dc6344381a</t>
+          <t>https://www.indeed.com/viewjob?jk=d716d1e9dd6e4b0b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Software Engineer III: Machine Learning Platform</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e5ace322ab3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=34e86f2f2a315595</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>SENIOR COMPUTER VISION ENGINEER – REMOTE SENSING</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Satlantis</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Gainesville, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101461b42f2929c7</t>
+          <t>https://www.indeed.com/viewjob?jk=74994cef74235bca</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>AI Platform Engineer - Associate</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
+          <t>https://www.indeed.com/viewjob?jk=2567cddf71e8f0fa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
+          <t>https://www.indeed.com/viewjob?jk=ee3c21dbe995c8b9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7364dc6344381a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,19 +1721,19 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a56c54d2027c92d</t>
+          <t>https://www.indeed.com/viewjob?jk=40e5ace322ab3dae</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11dd4db7d11a9ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=101461b42f2929c7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29610b7eba9cc4cb</t>
+          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693bc93cfe95e968</t>
+          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Architect (AWS, Azure, GCP)</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
+          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fafa6085d07ec220</t>
+          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71120e321dbd18c4</t>
+          <t>https://www.indeed.com/viewjob?jk=6a56c54d2027c92d</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be687a9701ed10cb</t>
+          <t>https://www.indeed.com/viewjob?jk=11dd4db7d11a9ebd</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Systems Administrator</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HH Brown Shoe Company</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Martinsburg, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bca63db22516c1c</t>
+          <t>https://www.indeed.com/viewjob?jk=29610b7eba9cc4cb</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
+          <t>https://www.indeed.com/viewjob?jk=693bc93cfe95e968</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Healthix</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51729f31816ec17</t>
+          <t>https://www.indeed.com/viewjob?jk=fafa6085d07ec220</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4efec6d9008a5b85</t>
+          <t>https://www.indeed.com/viewjob?jk=71120e321dbd18c4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Senior Data Architect (AWS, Azure, GCP)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Dataflow, HBase, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ea3f0ee7726aea</t>
+          <t>https://www.indeed.com/viewjob?jk=be687a9701ed10cb</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Java Architect</t>
+          <t>Systems Administrator</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HH Brown Shoe Company</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Martinsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34601ff78d0fbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=0bca63db22516c1c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Spring/Spring Boot Architect</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe5d1444b8c11690</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Java Architect</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Healthix</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ff0ce794c90e055</t>
+          <t>https://www.indeed.com/viewjob?jk=b51729f31816ec17</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Backend - AI Search</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16388829699da902</t>
+          <t>https://www.indeed.com/viewjob?jk=4efec6d9008a5b85</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,24 +2271,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
+          <t>https://www.indeed.com/viewjob?jk=03ea3f0ee7726aea</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Java Consultant</t>
+          <t>Java Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2306,77 +2306,77 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=e34601ff78d0fbb8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Spring/Spring Boot Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab66e7fa68e90c6</t>
+          <t>https://www.indeed.com/viewjob?jk=fe5d1444b8c11690</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Java Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50effdd5410c6590</t>
+          <t>https://www.indeed.com/viewjob?jk=8ff0ce794c90e055</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Snowflake/dbt/Healthcare) - 100% Remote</t>
+          <t>Cloud Identity Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Blue Sky Technology Solutions LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,129 +2421,129 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e0e6e4a15258683</t>
+          <t>https://www.indeed.com/viewjob?jk=f892a7ff9f3b3673</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Junior Software Development Engineer</t>
+          <t>Senior Software Engineer II - Backend - AI Search</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
+          <t>https://www.indeed.com/viewjob?jk=16388829699da902</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
+          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics</t>
+          <t>Java Consultant</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CX Data Labs</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
+          <t>https://www.indeed.com/viewjob?jk=64b708c3e0be0da7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Spring/Spring Boot Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,42 +2586,42 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e62470d61b3dfe4f</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab66e7fa68e90c6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
+          <t>Senior Databricks Developer / Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>TruStartIT LLC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, Oracle, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,67 +2631,67 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfe4e0f23d35bf4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Operations Analytics Data Scientist</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RadNet</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=50effdd5410c6590</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Data Engineer (Snowflake/dbt/Healthcare) - 100% Remote</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Northwestern Mutual</t>
+          <t>Blue Sky Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, ELT, dbt, Power BI, Tableau, CI/CD, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12eceb4f7778f690</t>
+          <t>https://www.indeed.com/viewjob?jk=2e0e6e4a15258683</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Junior Software Development Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Goodwill Industries of Ky., Inc.</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c96bce5537ab08e</t>
+          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior</t>
+          <t>Senior Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00e725f72169245</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Senior Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Vector Database Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Kimco Realty Corporation</t>
+          <t>Hanger</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,94 +2876,94 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Application Developer Sr II</t>
+          <t>Senior Architect, Data Engineering</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
+          <t>https://www.indeed.com/viewjob?jk=ff9e78b6f0cfc04d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Application Developer Sr I</t>
+          <t>Spring/Spring Boot Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
+          <t>https://www.indeed.com/viewjob?jk=e62470d61b3dfe4f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer Palantir</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Open Lending</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Polars, Power BI, Tableau, MLOps</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=980979d9074d5784</t>
+          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Open Lending</t>
+          <t>Charles River Laboratories</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Polars, Power BI, Tableau, MLOps</t>
+          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, HDFS, Hive, Sqoop, Spark</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46dca6f38ea157d1</t>
+          <t>https://www.indeed.com/viewjob?jk=dfbc6125913efbc5</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
+          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Operations Analytics Data Scientist</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>RadNet</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
+          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Northwestern Mutual</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Snowflake, ELT, dbt, Power BI, Tableau, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
+          <t>https://www.indeed.com/viewjob?jk=12eceb4f7778f690</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Goodwill Industries of Ky., Inc.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,112 +3146,112 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=6c96bce5537ab08e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Full Stack Engineer, Senior</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SiriusXM</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
+          <t>https://www.indeed.com/viewjob?jk=c00e725f72169245</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>adswizz</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
+          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Vector Database Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27aedc78511ea81</t>
+          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer New</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
+          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-AI</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
+          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
+          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Engineer Technology</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>AWS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,137 +3436,137 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
+          <t>https://www.indeed.com/viewjob?jk=0fb8d0b3951037c5</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
+          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
+          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Scala Architect</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcabbff9d7acb5a5</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>HealthEdge Software, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
+          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer (Hybrid)</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Westerra Credit Union</t>
+          <t>SiriusXM</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff473c63d82167e1</t>
+          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ML Platform Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>adswizz</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a246f2fce8506457</t>
+          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ML Platform Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=838425ec33e5fff1</t>
+          <t>https://www.indeed.com/viewjob?jk=b27aedc78511ea81</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ML Platform Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbf17f38d746779a</t>
+          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Machine Learning Engineer New</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Avaya</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,15 +3776,505 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer-AI</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Thomson Reuters</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Frisco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>SS&amp;C</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>AWS Network Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>TeraWatt Infrastructure</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>VeeRteq Solutions Inc.</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>AWS Network Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Data Engineer - Developer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Scala Architect</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dcabbff9d7acb5a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Business Intelligence Developer (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Westerra Credit Union</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff473c63d82167e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>HealthEdge Software, Inc.</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>ML Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a246f2fce8506457</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>ML Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=838425ec33e5fff1</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>ML Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbf17f38d746779a</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Avaya</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
           <t>RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, Git</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=93cc248964e1485d</t>
         </is>

--- a/results/job_matches_2026-03-17.xlsx
+++ b/results/job_matches_2026-03-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,95 +503,95 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=342faa6b5c9756a2</t>
+          <t>https://www.indeed.com/viewjob?jk=e53c61ac50aad63e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (ServiceNow)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hotwire Communications</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Scala, Kafka, Snowflake, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a28cfe9183e3c37</t>
+          <t>https://www.indeed.com/viewjob?jk=342faa6b5c9756a2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Senior Software Engineer (ServiceNow)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Hotwire Communications</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be2803455ebf096</t>
+          <t>https://www.indeed.com/viewjob?jk=8a28cfe9183e3c37</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tapouts</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Venice, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcb6f48928a08bed</t>
+          <t>https://www.indeed.com/viewjob?jk=5be2803455ebf096</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Glue</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tapouts</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Venice, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c8436cd0c6787a</t>
+          <t>https://www.indeed.com/viewjob?jk=bcb6f48928a08bed</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Software Engineer III - AWS Glue</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Arrow International</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25c3c576bdca9fea</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c8436cd0c6787a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Agile Developer - Datamart</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Arrow International</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, RDS, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b0a1eacc51b9571</t>
+          <t>https://www.indeed.com/viewjob?jk=25c3c576bdca9fea</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15708f0e06d200c6</t>
+          <t>https://www.indeed.com/viewjob?jk=8b0a1eacc51b9571</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Sr Agile Developer - Datamart</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,17 +801,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b271d311d5d546b6</t>
+          <t>https://www.indeed.com/viewjob?jk=15708f0e06d200c6</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ETL Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CPI Security</t>
+          <t>Hays</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Carolina, PR, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e81977d38af04d</t>
+          <t>https://www.indeed.com/viewjob?jk=233a1a341ad0aa38</t>
         </is>
       </c>
     </row>
@@ -1203,35 +1203,35 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ETL Data Engineer</t>
+          <t>Software Engineer III - AWS, Python, Spark</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hays</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Carolina, PR, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, Kafka, Oracle</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=233a1a341ad0aa38</t>
+          <t>https://www.indeed.com/viewjob?jk=17e1b01be240c764</t>
         </is>
       </c>
     </row>
@@ -1308,25 +1308,25 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Java Architect</t>
+          <t>Snowflake Architect Needed --- Local to Bay Area California</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deltasoft Solutions LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1e0df5a13808e32</t>
+          <t>https://www.indeed.com/viewjob?jk=db48c42eace691bd</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Snowflake Architect Needed --- Local to Bay Area California</t>
+          <t>Streaming Data</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Deltasoft Solutions LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Spark Streaming, Kafka, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db48c42eace691bd</t>
+          <t>https://www.indeed.com/viewjob?jk=1bf44e9b8dd895de</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Spark Streaming, Kafka, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bf44e9b8dd895de</t>
+          <t>https://www.indeed.com/viewjob?jk=d916292cc6da2afe</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (No Sponsorship Available)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Heritage Construction + Materials</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d916292cc6da2afe</t>
+          <t>https://www.indeed.com/viewjob?jk=8313f5120d5c6237</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer (No Sponsorship Available)</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Heritage Construction + Materials</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, ELT, Tableau</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8313f5120d5c6237</t>
+          <t>https://www.indeed.com/viewjob?jk=d716d1e9dd6e4b0b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Software Engineer III: Machine Learning Platform</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d716d1e9dd6e4b0b</t>
+          <t>https://www.indeed.com/viewjob?jk=34e86f2f2a315595</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer III: Machine Learning Platform</t>
+          <t>SENIOR COMPUTER VISION ENGINEER – REMOTE SENSING</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Satlantis</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Gainesville, FL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34e86f2f2a315595</t>
+          <t>https://www.indeed.com/viewjob?jk=74994cef74235bca</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SENIOR COMPUTER VISION ENGINEER – REMOTE SENSING</t>
+          <t>AI Platform Engineer - Associate</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Satlantis</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Gainesville, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74994cef74235bca</t>
+          <t>https://www.indeed.com/viewjob?jk=2567cddf71e8f0fa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Platform Engineer - Associate</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2567cddf71e8f0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=ee3c21dbe995c8b9</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee3c21dbe995c8b9</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7364dc6344381a</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7364dc6344381a</t>
+          <t>https://www.indeed.com/viewjob?jk=40e5ace322ab3dae</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e5ace322ab3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=101461b42f2929c7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101461b42f2929c7</t>
+          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3469bf400adaba5</t>
+          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
         </is>
       </c>
     </row>
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f82e84fba6f2d13</t>
+          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>AI &amp; Cloud Platform Consultant Expert</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Kafka, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, Scala, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=435cfd216c0dbc26</t>
+          <t>https://www.indeed.com/viewjob?jk=03afdcd6cea2e3b1</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Systems Administrator</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HH Brown Shoe Company</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Martinsburg, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Docker</t>
+          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bca63db22516c1c</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Healthix</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, GCP, Dataflow, Scala, Kafka, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb76bfe53b97698</t>
+          <t>https://www.indeed.com/viewjob?jk=b51729f31816ec17</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Healthix</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, SQL Server, NoSQL, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51729f31816ec17</t>
+          <t>https://www.indeed.com/viewjob?jk=4efec6d9008a5b85</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Engineer II - Backend - AI Search</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Seismic</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4efec6d9008a5b85</t>
+          <t>https://www.indeed.com/viewjob?jk=16388829699da902</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,42 +2271,42 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ea3f0ee7726aea</t>
+          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Java Architect</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CX Data Labs</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,67 +2316,67 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34601ff78d0fbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=64b708c3e0be0da7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Spring/Spring Boot Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe5d1444b8c11690</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab66e7fa68e90c6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Java Architect</t>
+          <t>Senior Databricks Developer / Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TruStartIT LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, Oracle, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ff0ce794c90e055</t>
+          <t>https://www.indeed.com/viewjob?jk=ecfe4e0f23d35bf4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cloud Identity Architect</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,129 +2421,129 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f892a7ff9f3b3673</t>
+          <t>https://www.indeed.com/viewjob?jk=50effdd5410c6590</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Backend - AI Search</t>
+          <t>Senior Data Engineer (Snowflake/dbt/Healthcare) - 100% Remote</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Seismic</t>
+          <t>Blue Sky Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Snowflake, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16388829699da902</t>
+          <t>https://www.indeed.com/viewjob?jk=2e0e6e4a15258683</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Junior Software Development Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7e33c6678441d2</t>
+          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Java Consultant</t>
+          <t>Senior Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032bac0300438f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Data Engineer - Analytics</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CX Data Labs</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b708c3e0be0da7</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab66e7fa68e90c6</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer / Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TruStartIT LLC</t>
+          <t>Hanger</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,42 +2621,42 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Scala, Kafka, Oracle, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecfe4e0f23d35bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Engineer Palantir</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50effdd5410c6590</t>
+          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Snowflake/dbt/Healthcare) - 100% Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Blue Sky Technology Solutions LLC</t>
+          <t>Charles River Laboratories</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, HDFS, Hive, Sqoop, Spark</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,19 +2701,19 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e0e6e4a15258683</t>
+          <t>https://www.indeed.com/viewjob?jk=dfbc6125913efbc5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Junior Software Development Engineer</t>
+          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2722,11 +2722,11 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, CI/CD, Jenkins, Docker, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2fe164c21da5777</t>
+          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics</t>
+          <t>Operations Analytics Data Scientist</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>RadNet</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b286e8aab1c0d5</t>
+          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Analytics</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Northwestern Mutual</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, GCP, BigQuery, Scala, ETL</t>
+          <t>AWS, RDS, Snowflake, ELT, dbt, Power BI, Tableau, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecf529675b29a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=12eceb4f7778f690</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Goodwill Industries of Ky., Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,67 +2841,67 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8d51cca35c142a</t>
+          <t>https://www.indeed.com/viewjob?jk=6c96bce5537ab08e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Full Stack Engineer, Senior</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Hanger</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a7763cc6047d702</t>
+          <t>https://www.indeed.com/viewjob?jk=c00e725f72169245</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Architect, Data Engineering</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Sqoop, Flume, Spark, Scala</t>
+          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,14 +2911,14 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff9e78b6f0cfc04d</t>
+          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Spring/Spring Boot Architect</t>
+          <t>Vector Database Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2932,11 +2932,11 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e62470d61b3dfe4f</t>
+          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer Palantir</t>
+          <t>Data Ops Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, Spark, PySpark, Snowflake, ETL</t>
+          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d50de78a56f1445</t>
+          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Charles River Laboratories</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, HDFS, Hive, Sqoop, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfbc6125913efbc5</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EverCommerce - Data Engineering Internship (Remote, US)</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1c2c847575eb45e</t>
+          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Operations Analytics Data Scientist</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>RadNet</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, MLOps, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=075a941875340eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Northwestern Mutual</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, ELT, dbt, Power BI, Tableau, CI/CD, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12eceb4f7778f690</t>
+          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Goodwill Industries of Ky., Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c96bce5537ab08e</t>
+          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full Stack Engineer, Senior</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00e725f72169245</t>
+          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Data Analytics &amp; BI with Tableau</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Google Cloud Platform, Scala, Kafka, Oracle, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af21e47bcc863fe</t>
+          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Vector Database Engineer</t>
+          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,102 +3261,102 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc525900a1b67460</t>
+          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>SiriusXM</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed87bc5ed02384b</t>
+          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>adswizz</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adae79f36f3017c</t>
+          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Kafka, CI/CD, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bad711dba26cd79</t>
+          <t>https://www.indeed.com/viewjob?jk=3abd3ae71d8f87b6</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - ML/AI Digital Workplace Experience</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, MLOps, CI/CD</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13da579f2549d25f</t>
+          <t>https://www.indeed.com/viewjob?jk=b27aedc78511ea81</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Engineer Technology</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fb8d0b3951037c5</t>
+          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DATA WAREHOUSE BUSINESS ANALYST</t>
+          <t>Machine Learning Engineer New</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Snowflake, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c96a3166ccc3279a</t>
+          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Senior Platform Engineer-AI</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e8e4b6ccf822c4</t>
+          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Ops Engineer</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Azure, Databricks, HDFS, Hive, Oozie, Impala, Spark, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ad5647756056444</t>
+          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd7a43792394b59b</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; BI with Tableau</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>TeraWatt Infrastructure</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Databricks, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeacb1d14bcd4d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Associate Software Engineer, Platform – COCore</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SiriusXM</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>AWS, Lambda, Athena, S3, RDS, Spark, Oracle, PostgreSQL, Terraform, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0fc6292598e8305</t>
+          <t>https://www.indeed.com/viewjob?jk=99ed0d4d942ded9c</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Software Engineer - API Solutions</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>adswizz</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Spark, Scala, Data Modeling, ETL, Tableau, Airflow</t>
+          <t>AWS, Athena, API Gateway, ECS, RDS, Spark, Scala, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfcb96820a6677d7</t>
+          <t>https://www.indeed.com/viewjob?jk=7bcf2915fd9bd1ef</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Software Engineer – Client Service</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Fanatics</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27aedc78511ea81</t>
+          <t>https://www.indeed.com/viewjob?jk=da07f3cfe8d1d836</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ede5f0e821359409</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer New</t>
+          <t>Data Engineer - Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57710bf99694ff8d</t>
+          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer-AI</t>
+          <t>Scala Architect</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Thomson Reuters</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec31862867bfb761</t>
+          <t>https://www.indeed.com/viewjob?jk=dcabbff9d7acb5a5</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Business Intelligence Developer (Hybrid)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Westerra Credit Union</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,437 +3846,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, IAM, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker, Kubernetes</t>
+          <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a3d5dba9944f59</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>AWS Network Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9a5c0072e4a559</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>TeraWatt Infrastructure</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac8657750172713</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>VeeRteq Solutions Inc.</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=586205a43fbcfd00</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>AWS Network Engineer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=85726105f14e77de</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Data Engineer - Developer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Redshift, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd500612ef29562e</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Scala Architect</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, NoSQL</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dcabbff9d7acb5a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Business Intelligence Developer (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Westerra Credit Union</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, Athena, RDS, Azure, Databricks, Scala, SQL Server, MySQL, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=ff473c63d82167e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>HealthEdge Software, Inc.</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc60e837a5ce034</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>ML Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a246f2fce8506457</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>ML Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=838425ec33e5fff1</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>ML Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fbf17f38d746779a</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Avaya</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=93cc248964e1485d</t>
         </is>
       </c>
     </row>
